--- a/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
+++ b/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="426">
   <si>
     <t>扬州旅行 · 最终方案首页</t>
   </si>
@@ -767,7 +767,7 @@
     <t>住宿候选</t>
   </si>
   <si>
-    <t>重点比较 6 人住两晚、环境、烧烤、房间床位与预订条件。</t>
+    <t>查看团队投票并比较 6 人住两晚、烧烤与房型；黄色“是否入选”可直接修改。</t>
   </si>
   <si>
     <t>名称</t>
@@ -818,6 +818,18 @@
     <t>推荐分</t>
   </si>
   <si>
+    <t>想去票</t>
+  </si>
+  <si>
+    <t>可以票</t>
+  </si>
+  <si>
+    <t>不考虑票</t>
+  </si>
+  <si>
+    <t>投票详情</t>
+  </si>
+  <si>
     <t>是否入选</t>
   </si>
   <si>
@@ -893,7 +905,7 @@
     <t>活动候选</t>
   </si>
   <si>
-    <t>密室、景点和其他团队活动；动态信息需在下单前复核。</t>
+    <t>查看团队投票、密室和景点条件；黄色“是否入选”可直接修改。</t>
   </si>
   <si>
     <t>活动类型</t>
@@ -1025,7 +1037,7 @@
     <t>餐饮候选</t>
   </si>
   <si>
-    <t>周六早茶、周日早餐、正餐与烧烤相关候选。</t>
+    <t>查看团队投票和餐饮候选；黄色“是否入选”可直接修改。</t>
   </si>
   <si>
     <t>适合安排</t>
@@ -1070,7 +1082,7 @@
     <t>攻略文章</t>
   </si>
   <si>
-    <t>攻略文章中已经提取的事实、建议与仍待核实的信息。</t>
+    <t>查看攻略摘要、团队投票和缺失信息；黄色“是否入选”可直接修改。</t>
   </si>
   <si>
     <t>标题</t>
@@ -1296,7 +1308,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1388,6 +1400,12 @@
       <sz val="10"/>
       <name val="PingFang SC"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="8A542C"/>
+      <sz val="9"/>
+      <name val="PingFang SC"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1472,7 +1490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1533,6 +1551,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3090,27 +3111,27 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3121,18 +3142,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3143,7 +3164,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3154,40 +3175,40 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3195,43 +3216,43 @@
         <v>91</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B12" s="20" t="s">
         <v>130</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>218</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -3262,115 +3283,115 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B5" s="14">
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B6" s="20">
         <v>3</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B8" s="20">
         <v>10</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B9" s="14">
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B10" s="20">
         <v>6</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -3853,7 +3874,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3872,12 +3893,12 @@
     <col min="19" max="21" width="16" customWidth="1"/>
     <col min="22" max="23" width="30" customWidth="1"/>
     <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="36" customWidth="1"/>
-    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="25" max="29" width="18" customWidth="1"/>
+    <col min="30" max="30" width="36" customWidth="1"/>
+    <col min="31" max="31" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>246</v>
       </c>
@@ -3907,8 +3928,12 @@
       <c r="Y1" s="17"/>
       <c r="Z1" s="17"/>
       <c r="AA1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>247</v>
       </c>
@@ -3938,8 +3963,12 @@
       <c r="Y2" s="18"/>
       <c r="Z2" s="18"/>
       <c r="AA2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>155</v>
       </c>
@@ -4016,99 +4045,126 @@
         <v>264</v>
       </c>
       <c r="Z3" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA3" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="AC3" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AD3" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="AA3" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AE3" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E4" s="20">
         <v>520</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M4" s="20" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N4" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q4" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="O4" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="P4" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>274</v>
-      </c>
       <c r="R4" s="20" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="T4" s="20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="U4" s="20" t="s">
         <v>86</v>
       </c>
       <c r="V4" s="20" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="W4" s="20" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="X4" s="20">
         <v>4.1</v>
       </c>
-      <c r="Y4" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20" t="s">
-        <v>287</v>
+      <c r="Y4" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD4" s="20"/>
+      <c r="AE4" s="20" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AA4"/>
+  <autoFilter ref="A3:AE4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A1:AE1"/>
+    <mergeCell ref="A2:AE2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="AC4">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4122,7 +4178,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4136,14 +4192,14 @@
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="15" width="30" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="36" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="17" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="36" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4163,10 +4219,14 @@
       <c r="Q1" s="17"/>
       <c r="R1" s="17"/>
       <c r="S1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -4186,8 +4246,12 @@
       <c r="Q2" s="18"/>
       <c r="R2" s="18"/>
       <c r="S2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>155</v>
       </c>
@@ -4195,7 +4259,7 @@
         <v>248</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>249</v>
@@ -4204,25 +4268,25 @@
         <v>31</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M3" s="19" t="s">
         <v>67</v>
@@ -4240,130 +4304,162 @@
         <v>264</v>
       </c>
       <c r="R3" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="U3" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="V3" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="S3" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="W3" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>99</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F4" s="20"/>
       <c r="G4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M4" s="20" t="s">
         <v>78</v>
       </c>
       <c r="N4" s="20" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="P4" s="20">
         <v>4.8</v>
       </c>
-      <c r="Q4" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q4" s="20">
+        <v>0</v>
+      </c>
+      <c r="R4" s="20">
+        <v>0</v>
+      </c>
+      <c r="S4" s="20">
+        <v>0</v>
+      </c>
+      <c r="T4" s="20"/>
+      <c r="U4" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>99</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F5" s="14">
         <v>0</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M5" s="14" t="s">
         <v>78</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="P5" s="14">
         <v>4.3</v>
       </c>
-      <c r="Q5" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q5" s="14">
+        <v>0</v>
+      </c>
+      <c r="R5" s="14">
+        <v>0</v>
+      </c>
+      <c r="S5" s="14">
+        <v>0</v>
+      </c>
+      <c r="T5" s="14"/>
+      <c r="U5" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>99</v>
@@ -4376,46 +4472,56 @@
       </c>
       <c r="F6" s="20"/>
       <c r="G6" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M6" s="20" t="s">
         <v>78</v>
       </c>
       <c r="N6" s="20" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="P6" s="20">
         <v>4.6</v>
       </c>
-      <c r="Q6" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q6" s="20">
+        <v>0</v>
+      </c>
+      <c r="R6" s="20">
+        <v>0</v>
+      </c>
+      <c r="S6" s="20">
+        <v>0</v>
+      </c>
+      <c r="T6" s="20"/>
+      <c r="U6" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>142</v>
@@ -4424,113 +4530,138 @@
         <v>99</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F7" s="14">
         <v>0</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M7" s="14" t="s">
         <v>78</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="P7" s="14">
         <v>4.7</v>
       </c>
-      <c r="Q7" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q7" s="14">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
+      </c>
+      <c r="S7" s="14">
+        <v>0</v>
+      </c>
+      <c r="T7" s="14"/>
+      <c r="U7" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>129</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="20" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M8" s="20" t="s">
         <v>86</v>
       </c>
       <c r="N8" s="20" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="P8" s="20">
         <v>3.8</v>
       </c>
-      <c r="Q8" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20" t="s">
-        <v>331</v>
+      <c r="Q8" s="20">
+        <v>0</v>
+      </c>
+      <c r="R8" s="20">
+        <v>0</v>
+      </c>
+      <c r="S8" s="20">
+        <v>0</v>
+      </c>
+      <c r="T8" s="20"/>
+      <c r="U8" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S8"/>
+  <autoFilter ref="A3:W8"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="U4:U8">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4544,7 +4675,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4558,14 +4689,14 @@
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="13" width="30" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="36" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="15" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="36" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4583,10 +4714,14 @@
       <c r="O1" s="17"/>
       <c r="P1" s="17"/>
       <c r="Q1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -4604,8 +4739,12 @@
       <c r="O2" s="18"/>
       <c r="P2" s="18"/>
       <c r="Q2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>155</v>
       </c>
@@ -4616,7 +4755,7 @@
         <v>61</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>249</v>
@@ -4625,19 +4764,19 @@
         <v>31</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>67</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="L3" s="19" t="s">
         <v>261</v>
@@ -4652,18 +4791,30 @@
         <v>264</v>
       </c>
       <c r="P3" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="T3" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="Q3" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U3" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>136</v>
@@ -4672,49 +4823,64 @@
         <v>92</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G4" s="20">
         <v>80</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J4" s="20" t="s">
         <v>86</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M4" s="20" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N4" s="20">
         <v>4.4</v>
       </c>
-      <c r="O4" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20" t="s">
-        <v>346</v>
+      <c r="O4" s="20">
+        <v>0</v>
+      </c>
+      <c r="P4" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>0</v>
+      </c>
+      <c r="R4" s="20"/>
+      <c r="S4" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q4"/>
+  <autoFilter ref="A3:U4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="S4">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4728,21 +4894,21 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="9" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="36" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4754,10 +4920,14 @@
       <c r="I1" s="17"/>
       <c r="J1" s="17"/>
       <c r="K1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -4769,25 +4939,29 @@
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>203</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>201</v>
@@ -4799,18 +4973,30 @@
         <v>264</v>
       </c>
       <c r="J3" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="N3" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="K3" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O3" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>9</v>
@@ -4819,10 +5005,10 @@
         <v>217</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>215</v>
@@ -4830,34 +5016,44 @@
       <c r="H4" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="I4" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="J4" s="20" t="s">
+      <c r="I4" s="20">
+        <v>0</v>
+      </c>
+      <c r="J4" s="20">
+        <v>0</v>
+      </c>
+      <c r="K4" s="20">
+        <v>0</v>
+      </c>
+      <c r="L4" s="20"/>
+      <c r="M4" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="N4" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="20" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O4" s="20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>226</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>224</v>
@@ -4865,19 +5061,29 @@
       <c r="H5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14"/>
+      <c r="M5" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="N5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O5" s="14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>232</v>
@@ -4889,10 +5095,10 @@
         <v>233</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>215</v>
@@ -4900,22 +5106,37 @@
       <c r="H6" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="J6" s="20" t="s">
+      <c r="I6" s="20">
+        <v>0</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0</v>
+      </c>
+      <c r="K6" s="20">
+        <v>0</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="N6" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>363</v>
+      <c r="O6" s="20" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K6"/>
+  <autoFilter ref="A3:O6"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="M4:M6">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4944,7 +5165,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4961,7 +5182,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -4990,10 +5211,10 @@
         <v>61</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>31</v>
@@ -5002,16 +5223,16 @@
         <v>65</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>67</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M3" s="19" t="s">
         <v>68</v>
@@ -5454,7 +5675,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -5466,7 +5687,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>

--- a/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
+++ b/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="行程首页" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="链接汇总" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="处理报告" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="住宿候选" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="活动候选" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="餐饮候选" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="攻略文章" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="两日行程" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="预订清单" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="项目设置" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="项目总览" state="visible" r:id="rId14"/>
+    <sheet sheetId="2" name="候选决策台" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="链接汇总" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="处理报告" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="住宿候选" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="活动候选" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="餐饮候选" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="攻略文章" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="两日行程" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="预订清单" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="项目设置" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="项目总览" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'行程首页'!$A1:$L48</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="469">
   <si>
     <t>扬州旅行 · 最终方案首页</t>
   </si>
@@ -599,6 +600,294 @@
     <t>以官方开放时间和预约规则为准</t>
   </si>
   <si>
+    <t>候选决策台</t>
+  </si>
+  <si>
+    <t>优先在这里筛选：比较价格、位置、核心规格和缺失项；黄色“人工结论 / 是否入选 / 人工备注”可直接修改。</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>区域 / 位置</t>
+  </si>
+  <si>
+    <t>参考价格</t>
+  </si>
+  <si>
+    <t>核心规格</t>
+  </si>
+  <si>
+    <t>主要亮点</t>
+  </si>
+  <si>
+    <t>主要风险</t>
+  </si>
+  <si>
+    <t>资料完整度</t>
+  </si>
+  <si>
+    <t>缺失信息</t>
+  </si>
+  <si>
+    <t>AI推荐分</t>
+  </si>
+  <si>
+    <t>想去票</t>
+  </si>
+  <si>
+    <t>可以票</t>
+  </si>
+  <si>
+    <t>不考虑票</t>
+  </si>
+  <si>
+    <t>人工结论</t>
+  </si>
+  <si>
+    <t>是否入选</t>
+  </si>
+  <si>
+    <t>人工备注</t>
+  </si>
+  <si>
+    <t>原始链接</t>
+  </si>
+  <si>
+    <t>place-001</t>
+  </si>
+  <si>
+    <t>瘦西湖</t>
+  </si>
+  <si>
+    <t>蜀冈—瘦西湖</t>
+  </si>
+  <si>
+    <t>票价待核实</t>
+  </si>
+  <si>
+    <t>约 3 小时</t>
+  </si>
+  <si>
+    <t>适合作为两日行程的第一站，游览节奏舒缓</t>
+  </si>
+  <si>
+    <t>旺季人流、票价和开放时间需要出发前核实</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；价格；适合人数；营业时间；预约要求；取消政策</t>
+  </si>
+  <si>
+    <t>拟定</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>place-004</t>
+  </si>
+  <si>
+    <t>运河三湾</t>
+  </si>
+  <si>
+    <t>¥0</t>
+  </si>
+  <si>
+    <t>内容丰富且适合作为第二天下午的室内安排</t>
+  </si>
+  <si>
+    <t>预约名额、闭馆日和入馆要求必须提前确认</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；适合人数；营业时间；预约要求；取消政策</t>
+  </si>
+  <si>
+    <t>place-003</t>
+  </si>
+  <si>
+    <t>个园</t>
+  </si>
+  <si>
+    <t>约 1.5 小时</t>
+  </si>
+  <si>
+    <t>与东关街距离近，适合组成紧凑的老城半日路线</t>
+  </si>
+  <si>
+    <t>讲解和预约政策需要查阅正式来源</t>
+  </si>
+  <si>
+    <t>place-006</t>
+  </si>
+  <si>
+    <t>扬州早茶候选</t>
+  </si>
+  <si>
+    <t>老城 / 瘦西湖周边</t>
+  </si>
+  <si>
+    <t>¥80</t>
+  </si>
+  <si>
+    <t>周六早茶；核对能否提前排号或预约</t>
+  </si>
+  <si>
+    <t>适合成为扬州行程的开场体验</t>
+  </si>
+  <si>
+    <t>具体门店、排队情况和人均价格需要真实链接比较</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；营业时间</t>
+  </si>
+  <si>
+    <t>place-002</t>
+  </si>
+  <si>
+    <t>东关街与东圈门</t>
+  </si>
+  <si>
+    <t>扬州老城</t>
+  </si>
+  <si>
+    <t>约 2 小时</t>
+  </si>
+  <si>
+    <t>适合把晚餐、散步和采购伴手礼放在一起</t>
+  </si>
+  <si>
+    <t>热门时段可能拥挤，网红商户仍需单独筛选</t>
+  </si>
+  <si>
+    <t>place-3380833f-f6d0-41eb-9718-7edde5088a6d</t>
+  </si>
+  <si>
+    <t>攻略</t>
+  </si>
+  <si>
+    <t>扬州美食攻略｜10大bi吃</t>
+  </si>
+  <si>
+    <t>待核实</t>
+  </si>
+  <si>
+    <t>扬州美食；扬州旅游攻略；扬州必吃；江浙沪周边游</t>
+  </si>
+  <si>
+    <t>涵盖经典扬州美食</t>
+  </si>
+  <si>
+    <t>未包含所有美食，评论区可补充</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实</t>
+  </si>
+  <si>
+    <t>待比较</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>http://xhslink.com/o/5HrEeOTXkGr</t>
+  </si>
+  <si>
+    <t>place-b34f514c-cc18-49a3-873b-8651853e07b9</t>
+  </si>
+  <si>
+    <t>扬州市</t>
+  </si>
+  <si>
+    <t>江苏省</t>
+  </si>
+  <si>
+    <t>历史文化；美食；园林；运河</t>
+  </si>
+  <si>
+    <t>美食之都</t>
+  </si>
+  <si>
+    <t>部分信息待核实</t>
+  </si>
+  <si>
+    <t>住宿；活动；餐饮具体信息；主要风险</t>
+  </si>
+  <si>
+    <t>https://zh.wikipedia.org/wiki/%E6%89%AC%E5%B7%9E%E5%B8%82</t>
+  </si>
+  <si>
+    <t>place-005</t>
+  </si>
+  <si>
+    <t>老城精品民宿候选</t>
+  </si>
+  <si>
+    <t>东关街周边</t>
+  </si>
+  <si>
+    <t>¥520</t>
+  </si>
+  <si>
+    <t>目标至少 3 个独立睡眠空间</t>
+  </si>
+  <si>
+    <t>靠近老城景点，可减少第一天晚间交通</t>
+  </si>
+  <si>
+    <t>仅为占位候选，房型、噪音和停车情况都要看真实链接</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；详细地址；6 人容量；户型；床位 / 床型；卫浴；烧烤；取消政策</t>
+  </si>
+  <si>
+    <t>place-007</t>
+  </si>
+  <si>
+    <t>团队密室候选</t>
+  </si>
+  <si>
+    <t>扬州市区</t>
+  </si>
+  <si>
+    <t>待团队投递</t>
+  </si>
+  <si>
+    <t>6 人；约 2 小时；中等优先；团队确认</t>
+  </si>
+  <si>
+    <t>可作为晚间或雨天的团队活动</t>
+  </si>
+  <si>
+    <t>暂无真实商户资料，需要补充密室链接后再比较</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；价格；营业时间；预约要求；取消政策</t>
+  </si>
+  <si>
+    <t>place-008</t>
+  </si>
+  <si>
+    <t>扬州两日慢游示例资料</t>
+  </si>
+  <si>
+    <t>不适用</t>
+  </si>
+  <si>
+    <t>路线框架；流程示例</t>
+  </si>
+  <si>
+    <t>提供了园林、老城和运河三条内容线索</t>
+  </si>
+  <si>
+    <t>并非真实攻略文章，正式使用时应由团队链接替换</t>
+  </si>
+  <si>
+    <t>https://example.com/yangzhou-guide</t>
+  </si>
+  <si>
     <t>链接汇总</t>
   </si>
   <si>
@@ -611,9 +900,6 @@
     <t>提交人</t>
   </si>
   <si>
-    <t>原始链接</t>
-  </si>
-  <si>
     <t>页面标题</t>
   </si>
   <si>
@@ -632,9 +918,6 @@
     <t>已提取信息</t>
   </si>
   <si>
-    <t>缺失信息</t>
-  </si>
-  <si>
     <t>AI摘要</t>
   </si>
   <si>
@@ -653,15 +936,9 @@
     <t>ykh</t>
   </si>
   <si>
-    <t>http://xhslink.com/o/5HrEeOTXkGr</t>
-  </si>
-  <si>
     <t>扬州美食攻略｜10大bi吃，有人同意吗？ - 小红书</t>
   </si>
   <si>
-    <t>攻略</t>
-  </si>
-  <si>
     <t>成功读取</t>
   </si>
   <si>
@@ -674,9 +951,6 @@
     <t>页面标题；内容分类；核心摘要</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实</t>
-  </si>
-  <si>
     <t>扬州10大必吃美食：扬州炒饭、三丁包、蟹粉狮子头、大煮干丝、文思豆腐、翡翠烧麦、千层油糕、扬州灌汤包、高邮咸鸭蛋、盐水鹅。</t>
   </si>
   <si>
@@ -692,9 +966,6 @@
     <t>Codex 流程测试</t>
   </si>
   <si>
-    <t>https://zh.wikipedia.org/wiki/%E6%89%AC%E5%B7%9E%E5%B8%82</t>
-  </si>
-  <si>
     <t>扬州市 - 维基百科，自由的百科全书</t>
   </si>
   <si>
@@ -719,12 +990,6 @@
     <t>系统示例</t>
   </si>
   <si>
-    <t>https://example.com/yangzhou-guide</t>
-  </si>
-  <si>
-    <t>扬州两日慢游示例资料</t>
-  </si>
-  <si>
     <t>示例资料：以瘦西湖、老城园林和运河博物馆串联两天路线。</t>
   </si>
   <si>
@@ -740,9 +1005,6 @@
     <t>快速查看哪些链接已成功整理、哪些未整理，以及缺失了什么。</t>
   </si>
   <si>
-    <t>分类</t>
-  </si>
-  <si>
     <t>结果说明</t>
   </si>
   <si>
@@ -767,24 +1029,39 @@
     <t>住宿候选</t>
   </si>
   <si>
-    <t>查看团队投票并比较 6 人住两晚、烧烤与房型；黄色“是否入选”可直接修改。</t>
-  </si>
-  <si>
-    <t>名称</t>
+    <t>民宿完整明细：价格、位置、户型、床位、烧烤、费用和取消政策；黄色列可直接修改。</t>
   </si>
   <si>
     <t>区域</t>
   </si>
   <si>
+    <t>地段特点</t>
+  </si>
+  <si>
+    <t>核心景点距离</t>
+  </si>
+  <si>
     <t>每晚价格</t>
   </si>
   <si>
+    <t>额外费用</t>
+  </si>
+  <si>
+    <t>押金</t>
+  </si>
+  <si>
+    <t>户型</t>
+  </si>
+  <si>
     <t>房间</t>
   </si>
   <si>
     <t>床位</t>
   </si>
   <si>
+    <t>床型</t>
+  </si>
+  <si>
     <t>卫浴</t>
   </si>
   <si>
@@ -809,6 +1086,12 @@
     <t>退房时间</t>
   </si>
   <si>
+    <t>取消政策</t>
+  </si>
+  <si>
+    <t>预订要求</t>
+  </si>
+  <si>
     <t>优点</t>
   </si>
   <si>
@@ -818,33 +1101,15 @@
     <t>推荐分</t>
   </si>
   <si>
-    <t>想去票</t>
-  </si>
-  <si>
-    <t>可以票</t>
-  </si>
-  <si>
-    <t>不考虑票</t>
+    <t>证据摘要</t>
   </si>
   <si>
     <t>投票详情</t>
   </si>
   <si>
-    <t>是否入选</t>
-  </si>
-  <si>
     <t>数据状态</t>
   </si>
   <si>
-    <t>place-005</t>
-  </si>
-  <si>
-    <t>老城精品民宿候选</t>
-  </si>
-  <si>
-    <t>东关街周边</t>
-  </si>
-  <si>
     <t>东关街周边（具体门牌待真实链接）</t>
   </si>
   <si>
@@ -854,15 +1119,9 @@
     <t>目标 6 人，实际容量待核实</t>
   </si>
   <si>
-    <t>目标至少 3 个独立睡眠空间</t>
-  </si>
-  <si>
     <t>床型与床数待核实</t>
   </si>
   <si>
-    <t>待核实</t>
-  </si>
-  <si>
     <t>环境好、安静、公共空间充足</t>
   </si>
   <si>
@@ -890,13 +1149,7 @@
     <t>周日，具体时间待核实</t>
   </si>
   <si>
-    <t>靠近老城景点，可减少第一天晚间交通</t>
-  </si>
-  <si>
-    <t>仅为占位候选，房型、噪音和停车情况都要看真实链接</t>
-  </si>
-  <si>
-    <t>否</t>
+    <t>等待团队提交真实民宿链接</t>
   </si>
   <si>
     <t>纯示例住宿，等待团队提交真实民宿</t>
@@ -905,7 +1158,7 @@
     <t>活动候选</t>
   </si>
   <si>
-    <t>查看团队投票、密室和景点条件；黄色“是否入选”可直接修改。</t>
+    <t>密室和景点完整明细：人数、价格、时长、难度、预约与取消政策；黄色列可直接修改。</t>
   </si>
   <si>
     <t>活动类型</t>
@@ -929,87 +1182,12 @@
     <t>预约要求</t>
   </si>
   <si>
-    <t>place-001</t>
-  </si>
-  <si>
-    <t>瘦西湖</t>
-  </si>
-  <si>
-    <t>蜀冈—瘦西湖</t>
-  </si>
-  <si>
-    <t>约 3 小时</t>
-  </si>
-  <si>
-    <t>适合作为两日行程的第一站，游览节奏舒缓</t>
-  </si>
-  <si>
-    <t>旺季人流、票价和开放时间需要出发前核实</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
     <t>流程示例，等待真实链接核实</t>
   </si>
   <si>
-    <t>place-002</t>
-  </si>
-  <si>
-    <t>东关街与东圈门</t>
-  </si>
-  <si>
-    <t>扬州老城</t>
-  </si>
-  <si>
-    <t>约 2 小时</t>
-  </si>
-  <si>
-    <t>适合把晚餐、散步和采购伴手礼放在一起</t>
-  </si>
-  <si>
-    <t>热门时段可能拥挤，网红商户仍需单独筛选</t>
-  </si>
-  <si>
-    <t>place-003</t>
-  </si>
-  <si>
-    <t>个园</t>
-  </si>
-  <si>
-    <t>约 1.5 小时</t>
-  </si>
-  <si>
-    <t>与东关街距离近，适合组成紧凑的老城半日路线</t>
-  </si>
-  <si>
-    <t>讲解和预约政策需要查阅正式来源</t>
-  </si>
-  <si>
-    <t>place-004</t>
-  </si>
-  <si>
-    <t>运河三湾</t>
-  </si>
-  <si>
-    <t>内容丰富且适合作为第二天下午的室内安排</t>
-  </si>
-  <si>
-    <t>预约名额、闭馆日和入馆要求必须提前确认</t>
-  </si>
-  <si>
     <t>流程示例，等待官方信息核实</t>
   </si>
   <si>
-    <t>place-007</t>
-  </si>
-  <si>
-    <t>团队密室候选</t>
-  </si>
-  <si>
-    <t>扬州市区</t>
-  </si>
-  <si>
     <t>扬州市区待选</t>
   </si>
   <si>
@@ -1025,19 +1203,13 @@
     <t>通常需预约，具体规则待真实链接</t>
   </si>
   <si>
-    <t>可作为晚间或雨天的团队活动</t>
-  </si>
-  <si>
-    <t>暂无真实商户资料，需要补充密室链接后再比较</t>
-  </si>
-  <si>
     <t>空位候选，等待真实密室链接</t>
   </si>
   <si>
     <t>餐饮候选</t>
   </si>
   <si>
-    <t>查看团队投票和餐饮候选；黄色“是否入选”可直接修改。</t>
+    <t>餐厅完整明细：人均、位置、营业时间、适合安排和预约要求；黄色列可直接修改。</t>
   </si>
   <si>
     <t>适合安排</t>
@@ -1049,15 +1221,6 @@
     <t>推荐菜/特点</t>
   </si>
   <si>
-    <t>place-006</t>
-  </si>
-  <si>
-    <t>扬州早茶候选</t>
-  </si>
-  <si>
-    <t>老城 / 瘦西湖周边</t>
-  </si>
-  <si>
     <t>老城 / 瘦西湖周边待选</t>
   </si>
   <si>
@@ -1070,19 +1233,13 @@
     <t>早茶；建议早到；门店待选</t>
   </si>
   <si>
-    <t>适合成为扬州行程的开场体验</t>
-  </si>
-  <si>
-    <t>具体门店、排队情况和人均价格需要真实链接比较</t>
-  </si>
-  <si>
     <t>流程示例，等待餐厅链接核实</t>
   </si>
   <si>
     <t>攻略文章</t>
   </si>
   <si>
-    <t>查看攻略摘要、团队投票和缺失信息；黄色“是否入选”可直接修改。</t>
+    <t>攻略完整明细：摘要、避坑、证据、缺失信息和团队意见；黄色列可直接修改。</t>
   </si>
   <si>
     <t>标题</t>
@@ -1097,34 +1254,7 @@
     <t>交通建议</t>
   </si>
   <si>
-    <t>place-3380833f-f6d0-41eb-9718-7edde5088a6d</t>
-  </si>
-  <si>
-    <t>扬州美食攻略｜10大bi吃</t>
-  </si>
-  <si>
-    <t>未包含所有美食，评论区可补充</t>
-  </si>
-  <si>
-    <t>place-b34f514c-cc18-49a3-873b-8651853e07b9</t>
-  </si>
-  <si>
-    <t>扬州市</t>
-  </si>
-  <si>
-    <t>江苏省</t>
-  </si>
-  <si>
-    <t>部分信息待核实</t>
-  </si>
-  <si>
     <t>partial</t>
-  </si>
-  <si>
-    <t>place-008</t>
-  </si>
-  <si>
-    <t>并非真实攻略文章，正式使用时应由团队链接替换</t>
   </si>
   <si>
     <t>纯示例攻略，等待真实文章链接</t>
@@ -1308,7 +1438,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="¥#,##0"/>
+  </numFmts>
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1406,6 +1540,11 @@
       <sz val="9"/>
       <name val="PingFang SC"/>
     </font>
+    <font>
+      <color rgb="8A542C"/>
+      <sz val="9"/>
+      <name val="PingFang SC"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1490,7 +1629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1540,20 +1679,59 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3102,6 +3280,240 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
@@ -3110,61 +3522,61 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="A1" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="A2" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>381</v>
+      <c r="A3" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>382</v>
+      <c r="C4" s="24" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>384</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="24">
         <v>6</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>385</v>
+      <c r="C6" s="24" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3175,40 +3587,40 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>389</v>
+      <c r="A8" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>394</v>
+      <c r="A10" s="24" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3216,43 +3628,43 @@
         <v>91</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="B12" s="20" t="s">
+      <c r="A12" s="24" t="s">
+        <v>440</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>398</v>
+      <c r="C12" s="24" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>218</v>
+        <v>309</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>400</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>403</v>
+      <c r="A14" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -3269,7 +3681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3282,116 +3694,116 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="A1" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="A2" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>381</v>
+      <c r="A3" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>410</v>
+      <c r="A4" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>411</v>
+        <v>454</v>
       </c>
       <c r="B5" s="14">
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B6" s="24">
         <v>3</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>414</v>
+      <c r="C6" s="24" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>415</v>
+        <v>458</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>416</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="24">
         <v>10</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>418</v>
+      <c r="C8" s="24" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="B9" s="14">
         <v>5</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" s="24">
         <v>6</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>422</v>
+      <c r="C10" s="24" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>423</v>
+        <v>466</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>424</v>
+        <v>467</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>425</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -3411,6 +3823,686 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="D9703E"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="13" style="17" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="12" style="18" customWidth="1"/>
+    <col min="12" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="18" max="18" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="25">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="K4" s="26">
+        <v>4.8</v>
+      </c>
+      <c r="L4" s="24">
+        <v>0</v>
+      </c>
+      <c r="M4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="24">
+        <v>0</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="I5" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="K5" s="29">
+        <v>4.7</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="I6" s="25">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="K6" s="26">
+        <v>4.6</v>
+      </c>
+      <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24">
+        <v>0</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="24"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="I7" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="K7" s="29">
+        <v>4.4</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="P7" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="14"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="I8" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="L8" s="24">
+        <v>0</v>
+      </c>
+      <c r="M8" s="24">
+        <v>0</v>
+      </c>
+      <c r="N8" s="24">
+        <v>0</v>
+      </c>
+      <c r="O8" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="P8" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="24"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="I9" s="30">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="29">
+        <v>4.5</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14">
+        <v>0</v>
+      </c>
+      <c r="N9" s="14">
+        <v>0</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P9" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="I10" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="K10" s="26">
+        <v>4.5</v>
+      </c>
+      <c r="L10" s="24">
+        <v>0</v>
+      </c>
+      <c r="M10" s="24">
+        <v>0</v>
+      </c>
+      <c r="N10" s="24">
+        <v>0</v>
+      </c>
+      <c r="O10" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P10" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="I11" s="25">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="K11" s="29">
+        <v>4.1</v>
+      </c>
+      <c r="L11" s="14">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14">
+        <v>0</v>
+      </c>
+      <c r="O11" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P11" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="14"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="I12" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="K12" s="26">
+        <v>3.8</v>
+      </c>
+      <c r="L12" s="24">
+        <v>0</v>
+      </c>
+      <c r="M12" s="24">
+        <v>0</v>
+      </c>
+      <c r="N12" s="24">
+        <v>0</v>
+      </c>
+      <c r="O12" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P12" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="24"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="I13" s="30">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="K13" s="29">
+        <v>3.5</v>
+      </c>
+      <c r="L13" s="14">
+        <v>0</v>
+      </c>
+      <c r="M13" s="14">
+        <v>0</v>
+      </c>
+      <c r="N13" s="14">
+        <v>0</v>
+      </c>
+      <c r="O13" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P13" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="O10:O13">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="O4:O13">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="P10:P13">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="P4:P13">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O6"/>
@@ -3424,225 +4516,226 @@
     <col min="6" max="9" width="16" customWidth="1"/>
     <col min="10" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="15" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
+      <c r="A1" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
+      <c r="A2" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="J3" s="19" t="s">
+      <c r="B3" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="K3" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="K3" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="O3" s="19" t="s">
+      <c r="L3" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
+      <c r="A4" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>220</v>
+        <v>311</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>221</v>
+        <v>312</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>214</v>
+        <v>306</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>226</v>
+        <v>316</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>218</v>
+        <v>309</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14" t="s">
-        <v>227</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20" t="s">
-        <v>235</v>
+      <c r="A6" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3659,7 +4752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3678,181 +4771,181 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="A1" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="A2" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="H3" s="19" t="s">
+      <c r="B3" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="I3" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="I3" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>240</v>
+      <c r="J3" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>242</v>
+      <c r="A4" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>221</v>
+        <v>312</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>243</v>
+        <v>330</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>244</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>245</v>
+      <c r="A6" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -3869,796 +4962,418 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AR4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="7" max="7" width="16" style="33" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="30" customWidth="1"/>
-    <col min="19" max="21" width="16" customWidth="1"/>
-    <col min="22" max="23" width="30" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="29" width="18" customWidth="1"/>
-    <col min="30" max="30" width="36" customWidth="1"/>
-    <col min="31" max="31" width="16" customWidth="1"/>
+    <col min="13" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="30" customWidth="1"/>
+    <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="30" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="16" customWidth="1"/>
+    <col min="30" max="31" width="30" customWidth="1"/>
+    <col min="32" max="32" width="16" style="18" customWidth="1"/>
+    <col min="33" max="33" width="18" style="17" customWidth="1"/>
+    <col min="34" max="35" width="30" customWidth="1"/>
+    <col min="36" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="30" customWidth="1"/>
+    <col min="43" max="43" width="36" customWidth="1"/>
+    <col min="44" max="44" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="1" ht="36" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+      <c r="AP1" s="19"/>
+      <c r="AQ1" s="19"/>
+      <c r="AR1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="AF3" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="AG3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="AL3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="AM3" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="AO3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="AP3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="AQ3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="AR3" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="J3" s="19" t="s">
+      <c r="F4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="G4" s="35">
+        <v>520</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="T4" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="W4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD4" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF4" s="26">
+        <v>4.1</v>
+      </c>
+      <c r="AG4" s="25">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AH4" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="AI4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="AJ4" s="24">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="24">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="24">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="24"/>
+      <c r="AN4" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="AO4" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="L3" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="S3" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="T3" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="V3" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="W3" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="X3" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y3" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="Z3" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA3" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="AC3" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="AD3" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE3" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="E4" s="20">
-        <v>520</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="N4" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="P4" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="R4" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="S4" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="T4" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="U4" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="V4" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="W4" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="X4" s="20">
-        <v>4.1</v>
-      </c>
-      <c r="Y4" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="20">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="AD4" s="20"/>
-      <c r="AE4" s="20" t="s">
-        <v>291</v>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="24"/>
+      <c r="AR4" s="24" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AE4"/>
+  <autoFilter ref="A3:AR4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AE1"/>
-    <mergeCell ref="A2:AE2"/>
+    <mergeCell ref="A1:AR1"/>
+    <mergeCell ref="A2:AR2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="AC4">
-      <formula1>"是,否"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="AN4">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:W8"/>
-  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="36" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="S3" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="T3" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="V3" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="W3" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="N4" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="P4" s="20">
-        <v>4.8</v>
-      </c>
-      <c r="Q4" s="20">
-        <v>0</v>
-      </c>
-      <c r="R4" s="20">
-        <v>0</v>
-      </c>
-      <c r="S4" s="20">
-        <v>0</v>
-      </c>
-      <c r="T4" s="20"/>
-      <c r="U4" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" s="14">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="P5" s="14">
-        <v>4.3</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>0</v>
-      </c>
-      <c r="R5" s="14">
-        <v>0</v>
-      </c>
-      <c r="S5" s="14">
-        <v>0</v>
-      </c>
-      <c r="T5" s="14"/>
-      <c r="U5" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="J6" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="P6" s="20">
-        <v>4.6</v>
-      </c>
-      <c r="Q6" s="20">
-        <v>0</v>
-      </c>
-      <c r="R6" s="20">
-        <v>0</v>
-      </c>
-      <c r="S6" s="20">
-        <v>0</v>
-      </c>
-      <c r="T6" s="20"/>
-      <c r="U6" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="P7" s="14">
-        <v>4.7</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>0</v>
-      </c>
-      <c r="R7" s="14">
-        <v>0</v>
-      </c>
-      <c r="S7" s="14">
-        <v>0</v>
-      </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="J8" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="P8" s="20">
-        <v>3.8</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>0</v>
-      </c>
-      <c r="R8" s="20">
-        <v>0</v>
-      </c>
-      <c r="S8" s="20">
-        <v>0</v>
-      </c>
-      <c r="T8" s="20"/>
-      <c r="U8" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20" t="s">
-        <v>335</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:W8"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A2:W2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="U4:U8">
+    <dataValidation type="list" sqref="AO4">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4675,209 +5390,605 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="13" width="30" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" style="33" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="36" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="15" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="16" style="18" customWidth="1"/>
+    <col min="18" max="18" width="18" style="17" customWidth="1"/>
+    <col min="19" max="20" width="30" customWidth="1"/>
+    <col min="21" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="30" customWidth="1"/>
+    <col min="28" max="28" width="36" customWidth="1"/>
+    <col min="29" max="29" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="1" ht="36" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="R3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="35"/>
+      <c r="G4" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="S3" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="T3" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="G4" s="20">
-        <v>80</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="J4" s="20" t="s">
+      <c r="H4" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q4" s="26">
+        <v>4.8</v>
+      </c>
+      <c r="R4" s="25">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="T4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="U4" s="24">
+        <v>0</v>
+      </c>
+      <c r="V4" s="24">
+        <v>0</v>
+      </c>
+      <c r="W4" s="24">
+        <v>0</v>
+      </c>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z4" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="36">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q5" s="29">
+        <v>4.3</v>
+      </c>
+      <c r="R5" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="U5" s="14">
+        <v>0</v>
+      </c>
+      <c r="V5" s="14">
+        <v>0</v>
+      </c>
+      <c r="W5" s="14">
+        <v>0</v>
+      </c>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z5" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="35"/>
+      <c r="G6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q6" s="26">
+        <v>4.6</v>
+      </c>
+      <c r="R6" s="25">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S6" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="T6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="U6" s="24">
+        <v>0</v>
+      </c>
+      <c r="V6" s="24">
+        <v>0</v>
+      </c>
+      <c r="W6" s="24">
+        <v>0</v>
+      </c>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z6" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" s="36">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q7" s="29">
+        <v>4.7</v>
+      </c>
+      <c r="R7" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="U7" s="14">
+        <v>0</v>
+      </c>
+      <c r="V7" s="14">
+        <v>0</v>
+      </c>
+      <c r="W7" s="14">
+        <v>0</v>
+      </c>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z7" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="35"/>
+      <c r="G8" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="N8" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="K4" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="N4" s="20">
-        <v>4.4</v>
-      </c>
-      <c r="O4" s="20">
+      <c r="O8" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q8" s="26">
+        <v>3.8</v>
+      </c>
+      <c r="R8" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S8" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="T8" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="U8" s="24">
         <v>0</v>
       </c>
-      <c r="P4" s="20">
+      <c r="V8" s="24">
         <v>0</v>
       </c>
-      <c r="Q4" s="20">
+      <c r="W8" s="24">
         <v>0</v>
       </c>
-      <c r="R4" s="20"/>
-      <c r="S4" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20" t="s">
-        <v>350</v>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z8" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:U4"/>
+  <autoFilter ref="A3:AC8"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A2:AC2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="S4">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="Y4:Y8">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Z4:Z8">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4894,246 +6005,263 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="8" width="30" customWidth="1"/>
-    <col min="9" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="36" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" style="33" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="14" width="30" customWidth="1"/>
+    <col min="15" max="15" width="16" style="18" customWidth="1"/>
+    <col min="16" max="16" width="18" style="17" customWidth="1"/>
+    <col min="17" max="18" width="30" customWidth="1"/>
+    <col min="19" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="30" customWidth="1"/>
+    <col min="26" max="26" width="36" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="1" ht="36" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="K3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="P3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="S3" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="T3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="V3" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="W3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="G4" s="35">
+        <v>80</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>400</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="O4" s="26">
+        <v>4.4</v>
+      </c>
+      <c r="P4" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="S4" s="24">
         <v>0</v>
       </c>
-      <c r="J4" s="20">
+      <c r="T4" s="24">
         <v>0</v>
       </c>
-      <c r="K4" s="20">
+      <c r="U4" s="24">
         <v>0</v>
       </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="N4" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="I5" s="14">
-        <v>0</v>
-      </c>
-      <c r="J5" s="14">
-        <v>0</v>
-      </c>
-      <c r="K5" s="14">
-        <v>0</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="I6" s="20">
-        <v>0</v>
-      </c>
-      <c r="J6" s="20">
-        <v>0</v>
-      </c>
-      <c r="K6" s="20">
-        <v>0</v>
-      </c>
-      <c r="L6" s="20"/>
-      <c r="M6" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>367</v>
+      <c r="V4" s="24"/>
+      <c r="W4" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O6"/>
+  <autoFilter ref="A3:AA4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:AA2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="M4:M6">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="W4">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="X4">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5146,6 +6274,318 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="18" style="17" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="18" max="18" width="36" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="I4" s="30">
+        <v>1</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K4" s="24">
+        <v>0</v>
+      </c>
+      <c r="L4" s="24">
+        <v>0</v>
+      </c>
+      <c r="M4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="24"/>
+      <c r="O4" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I5" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14"/>
+      <c r="O5" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P5" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="S5" s="14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="I6" s="30">
+        <v>1</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0</v>
+      </c>
+      <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24"/>
+      <c r="O6" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="S6" s="24" t="s">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:S6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="O4:O6">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="P4:P6">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5164,116 +6604,116 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="A1" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+      <c r="A2" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="E3" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="J3" s="19" t="s">
+      <c r="I3" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="M3" s="19" t="s">
+      <c r="K3" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="24">
         <v>30</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -5313,41 +6753,41 @@
       <c r="M5" s="14"/>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="24">
         <v>80</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -5387,41 +6827,41 @@
       <c r="M7" s="14"/>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="24">
         <v>0</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
@@ -5461,41 +6901,41 @@
       <c r="M9" s="14"/>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="24">
         <v>40</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
@@ -5535,41 +6975,41 @@
       <c r="M11" s="14"/>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="24">
         <v>100</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
@@ -5609,41 +7049,41 @@
       <c r="M13" s="14"/>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="24">
         <v>60</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="K14" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:M14"/>
@@ -5657,238 +7097,4 @@
     <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:H9"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
+++ b/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
@@ -9,13 +9,15 @@
     <sheet sheetId="3" name="链接汇总" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="处理报告" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="住宿候选" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="活动候选" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="餐饮候选" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="攻略文章" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="两日行程" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="预订清单" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="项目设置" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="项目总览" state="visible" r:id="rId15"/>
+    <sheet sheetId="6" name="美食餐饮" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="密室候选" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="室内休闲" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="景点户外" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="攻略文章" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="两日行程" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="预订清单" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="项目设置" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="项目总览" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'行程首页'!$A1:$L48</definedName>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="518">
   <si>
     <t>扬州旅行 · 最终方案首页</t>
   </si>
@@ -606,7 +608,10 @@
     <t>优先在这里筛选：比较价格、位置、核心规格和缺失项；黄色“人工结论 / 是否入选 / 人工备注”可直接修改。</t>
   </si>
   <si>
-    <t>分类</t>
+    <t>大类</t>
+  </si>
+  <si>
+    <t>子分类</t>
   </si>
   <si>
     <t>名称</t>
@@ -621,6 +626,9 @@
     <t>核心规格</t>
   </si>
   <si>
+    <t>特征标签</t>
+  </si>
+  <si>
     <t>主要亮点</t>
   </si>
   <si>
@@ -654,12 +662,18 @@
     <t>人工备注</t>
   </si>
   <si>
+    <t>人工保护字段</t>
+  </si>
+  <si>
     <t>原始链接</t>
   </si>
   <si>
     <t>place-001</t>
   </si>
   <si>
+    <t>园林景区</t>
+  </si>
+  <si>
     <t>瘦西湖</t>
   </si>
   <si>
@@ -669,16 +683,13 @@
     <t>票价待核实</t>
   </si>
   <si>
-    <t>约 3 小时</t>
-  </si>
-  <si>
     <t>适合作为两日行程的第一站，游览节奏舒缓</t>
   </si>
   <si>
     <t>旺季人流、票价和开放时间需要出发前核实</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实；价格；适合人数；营业时间；预约要求；取消政策</t>
+    <t>价格或预约等动态信息仍需核实；票价；开放时间；预约要求；天气影响</t>
   </si>
   <si>
     <t>拟定</t>
@@ -696,13 +707,16 @@
     <t>¥0</t>
   </si>
   <si>
+    <t>景点；室内；需要预约</t>
+  </si>
+  <si>
     <t>内容丰富且适合作为第二天下午的室内安排</t>
   </si>
   <si>
     <t>预约名额、闭馆日和入馆要求必须提前确认</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实；适合人数；营业时间；预约要求；取消政策</t>
+    <t>价格或预约等动态信息仍需核实；开放时间；预约要求；天气影响</t>
   </si>
   <si>
     <t>place-003</t>
@@ -711,9 +725,6 @@
     <t>个园</t>
   </si>
   <si>
-    <t>约 1.5 小时</t>
-  </si>
-  <si>
     <t>与东关街距离近，适合组成紧凑的老城半日路线</t>
   </si>
   <si>
@@ -723,6 +734,9 @@
     <t>place-006</t>
   </si>
   <si>
+    <t>早茶早餐</t>
+  </si>
+  <si>
     <t>扬州早茶候选</t>
   </si>
   <si>
@@ -732,7 +746,7 @@
     <t>¥80</t>
   </si>
   <si>
-    <t>周六早茶；核对能否提前排号或预约</t>
+    <t>餐饮；早茶早餐</t>
   </si>
   <si>
     <t>适合成为扬州行程的开场体验</t>
@@ -741,445 +755,616 @@
     <t>具体门店、排队情况和人均价格需要真实链接比较</t>
   </si>
   <si>
-    <t>价格或预约等动态信息仍需核实；营业时间</t>
+    <t>价格或预约等动态信息仍需核实；招牌菜；六人适合度；营业时间</t>
   </si>
   <si>
     <t>place-002</t>
   </si>
   <si>
+    <t>其他景点</t>
+  </si>
+  <si>
     <t>东关街与东圈门</t>
   </si>
   <si>
     <t>扬州老城</t>
   </si>
   <si>
+    <t>适合把晚餐、散步和采购伴手礼放在一起</t>
+  </si>
+  <si>
+    <t>热门时段可能拥挤，网红商户仍需单独筛选</t>
+  </si>
+  <si>
+    <t>place-3380833f-f6d0-41eb-9718-7edde5088a6d</t>
+  </si>
+  <si>
+    <t>攻略</t>
+  </si>
+  <si>
+    <t>美食攻略</t>
+  </si>
+  <si>
+    <t>扬州美食攻略｜10大bi吃</t>
+  </si>
+  <si>
+    <t>待核实</t>
+  </si>
+  <si>
+    <t>扬州美食；扬州旅游攻略；扬州必吃；江浙沪周边游</t>
+  </si>
+  <si>
+    <t>涵盖经典扬州美食</t>
+  </si>
+  <si>
+    <t>未包含所有美食，评论区可补充</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实</t>
+  </si>
+  <si>
+    <t>待比较</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>http://xhslink.com/o/5HrEeOTXkGr</t>
+  </si>
+  <si>
+    <t>place-b34f514c-cc18-49a3-873b-8651853e07b9</t>
+  </si>
+  <si>
+    <t>综合攻略</t>
+  </si>
+  <si>
+    <t>扬州市</t>
+  </si>
+  <si>
+    <t>江苏省</t>
+  </si>
+  <si>
+    <t>历史文化；美食；园林；运河</t>
+  </si>
+  <si>
+    <t>美食之都</t>
+  </si>
+  <si>
+    <t>部分信息待核实</t>
+  </si>
+  <si>
+    <t>住宿；活动；餐饮具体信息；主要风险</t>
+  </si>
+  <si>
+    <t>https://zh.wikipedia.org/wiki/%E6%89%AC%E5%B7%9E%E5%B8%82</t>
+  </si>
+  <si>
+    <t>place-005</t>
+  </si>
+  <si>
+    <t>民宿</t>
+  </si>
+  <si>
+    <t>老城精品民宿候选</t>
+  </si>
+  <si>
+    <t>东关街周边</t>
+  </si>
+  <si>
+    <t>¥520</t>
+  </si>
+  <si>
+    <t>目标至少 3 个独立睡眠空间</t>
+  </si>
+  <si>
+    <t>靠近老城景点，可减少第一天晚间交通</t>
+  </si>
+  <si>
+    <t>仅为占位候选，房型、噪音和停车情况都要看真实链接</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；详细地址；6 人容量；户型；床位 / 床型；卫浴；烧烤；取消政策</t>
+  </si>
+  <si>
+    <t>place-007</t>
+  </si>
+  <si>
+    <t>密室</t>
+  </si>
+  <si>
+    <t>未分类密室</t>
+  </si>
+  <si>
+    <t>团队密室候选</t>
+  </si>
+  <si>
+    <t>扬州市区</t>
+  </si>
+  <si>
+    <t>待团队投递</t>
+  </si>
+  <si>
+    <t>团队确认；中等优先</t>
+  </si>
+  <si>
+    <t>密室；需要预约</t>
+  </si>
+  <si>
+    <t>可作为晚间或雨天的团队活动</t>
+  </si>
+  <si>
+    <t>暂无真实商户资料，需要补充密室链接后再比较</t>
+  </si>
+  <si>
+    <t>价格或预约等动态信息仍需核实；单人价格；场地规模；六人独立开场；预约要求</t>
+  </si>
+  <si>
+    <t>place-008</t>
+  </si>
+  <si>
+    <t>行程攻略</t>
+  </si>
+  <si>
+    <t>扬州两日慢游示例资料</t>
+  </si>
+  <si>
+    <t>不适用</t>
+  </si>
+  <si>
+    <t>路线框架；流程示例</t>
+  </si>
+  <si>
+    <t>提供了园林、老城和运河三条内容线索</t>
+  </si>
+  <si>
+    <t>并非真实攻略文章，正式使用时应由团队链接替换</t>
+  </si>
+  <si>
+    <t>https://example.com/yangzhou-guide</t>
+  </si>
+  <si>
+    <t>链接汇总</t>
+  </si>
+  <si>
+    <t>每一条团队链接的完整台账；读取失败也会保留，不会静默丢失。</t>
+  </si>
+  <si>
+    <t>提交时间</t>
+  </si>
+  <si>
+    <t>提交人</t>
+  </si>
+  <si>
+    <t>页面标题</t>
+  </si>
+  <si>
+    <t>读取结果</t>
+  </si>
+  <si>
+    <t>整理结果</t>
+  </si>
+  <si>
+    <t>处理状态</t>
+  </si>
+  <si>
+    <t>已提取信息</t>
+  </si>
+  <si>
+    <t>AI摘要</t>
+  </si>
+  <si>
+    <t>分析模型</t>
+  </si>
+  <si>
+    <t>错误原因</t>
+  </si>
+  <si>
+    <t>link-0c57f71b3b10</t>
+  </si>
+  <si>
+    <t>2026-07-20T12:48:03.252Z</t>
+  </si>
+  <si>
+    <t>ykh</t>
+  </si>
+  <si>
+    <t>扬州美食攻略｜10大bi吃，有人同意吗？ - 小红书</t>
+  </si>
+  <si>
+    <t>成功读取</t>
+  </si>
+  <si>
+    <t>已整理</t>
+  </si>
+  <si>
+    <t>已写入Excel</t>
+  </si>
+  <si>
+    <t>页面标题；内容分类；核心摘要</t>
+  </si>
+  <si>
+    <t>扬州10大必吃美食：扬州炒饭、三丁包、蟹粉狮子头、大煮干丝、文思豆腐、翡翠烧麦、千层油糕、扬州灌汤包、高邮咸鸭蛋、盐水鹅。</t>
+  </si>
+  <si>
+    <t>DeepSeek · deepseek-v4-flash</t>
+  </si>
+  <si>
+    <t>link-df4b1ba42b06</t>
+  </si>
+  <si>
+    <t>2026-07-20T12:33:13.051Z</t>
+  </si>
+  <si>
+    <t>Codex 流程测试</t>
+  </si>
+  <si>
+    <t>扬州市 - 维基百科，自由的百科全书</t>
+  </si>
+  <si>
+    <t>扬州是首批国家历史文化名城；拥有瘦西湖、个园等景点；淮扬菜发源地</t>
+  </si>
+  <si>
+    <t>住宿；活动；餐饮具体信息</t>
+  </si>
+  <si>
+    <t>扬州是江苏省地级市，国家历史文化名城，以淮扬菜、园林和运河文化闻名，适合周末旅行。</t>
+  </si>
+  <si>
+    <t>验证 DeepSeek 解析并写入 Excel；测试完成后保留为示例资料</t>
+  </si>
+  <si>
+    <t>seed-guide-001</t>
+  </si>
+  <si>
+    <t>2026-07-20T02:00:00.000Z</t>
+  </si>
+  <si>
+    <t>系统示例</t>
+  </si>
+  <si>
+    <t>示例资料：以瘦西湖、老城园林和运河博物馆串联两天路线。</t>
+  </si>
+  <si>
+    <t>演示分析</t>
+  </si>
+  <si>
+    <t>用于演示完整流程，可在正式收集后删除</t>
+  </si>
+  <si>
+    <t>处理报告</t>
+  </si>
+  <si>
+    <t>快速查看哪些链接已成功整理、哪些未整理，以及缺失了什么。</t>
+  </si>
+  <si>
+    <t>结果说明</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>已生成候选资料并写入 Excel</t>
+  </si>
+  <si>
+    <t>2026-07-20T12:48:06.535Z</t>
+  </si>
+  <si>
+    <t>已整理；仍有 3 项待核实</t>
+  </si>
+  <si>
+    <t>2026-07-20T13:17:54.301Z</t>
+  </si>
+  <si>
+    <t>2026-07-20T02:02:00.000Z</t>
+  </si>
+  <si>
+    <t>住宿候选</t>
+  </si>
+  <si>
+    <t>民宿完整明细：价格、位置、户型、床位、烧烤、费用和取消政策；黄色列可直接修改。</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>地段特点</t>
+  </si>
+  <si>
+    <t>核心景点距离</t>
+  </si>
+  <si>
+    <t>每晚价格</t>
+  </si>
+  <si>
+    <t>额外费用</t>
+  </si>
+  <si>
+    <t>押金</t>
+  </si>
+  <si>
+    <t>户型</t>
+  </si>
+  <si>
+    <t>房间</t>
+  </si>
+  <si>
+    <t>床位</t>
+  </si>
+  <si>
+    <t>床型</t>
+  </si>
+  <si>
+    <t>卫浴</t>
+  </si>
+  <si>
+    <t>环境特点</t>
+  </si>
+  <si>
+    <t>是否整租</t>
+  </si>
+  <si>
+    <t>厨房</t>
+  </si>
+  <si>
+    <t>烧烤设备/费用</t>
+  </si>
+  <si>
+    <t>停车</t>
+  </si>
+  <si>
+    <t>入住时间</t>
+  </si>
+  <si>
+    <t>退房时间</t>
+  </si>
+  <si>
+    <t>取消政策</t>
+  </si>
+  <si>
+    <t>预订要求</t>
+  </si>
+  <si>
+    <t>优点</t>
+  </si>
+  <si>
+    <t>缺点</t>
+  </si>
+  <si>
+    <t>推荐分</t>
+  </si>
+  <si>
+    <t>证据摘要</t>
+  </si>
+  <si>
+    <t>投票详情</t>
+  </si>
+  <si>
+    <t>数据状态</t>
+  </si>
+  <si>
+    <t>东关街周边（具体门牌待真实链接）</t>
+  </si>
+  <si>
+    <t>日期和房源确认后计算</t>
+  </si>
+  <si>
+    <t>目标 6 人，实际容量待核实</t>
+  </si>
+  <si>
+    <t>床型与床数待核实</t>
+  </si>
+  <si>
+    <t>环境好、安静、公共空间充足</t>
+  </si>
+  <si>
+    <t>整租优先，待核实</t>
+  </si>
+  <si>
+    <t>希望可用，待核实</t>
+  </si>
+  <si>
+    <t>必须确认允许，当前未知</t>
+  </si>
+  <si>
+    <t>设备、炭火和清洁费待核实</t>
+  </si>
+  <si>
+    <t>不强求含早，周边早餐需方便</t>
+  </si>
+  <si>
+    <t>老城步行 / 打车便利优先</t>
+  </si>
+  <si>
+    <t>周五晚，具体时间待核实</t>
+  </si>
+  <si>
+    <t>周日，具体时间待核实</t>
+  </si>
+  <si>
+    <t>等待团队提交真实民宿链接</t>
+  </si>
+  <si>
+    <t>纯示例住宿，等待团队提交真实民宿</t>
+  </si>
+  <si>
+    <t>美食餐饮</t>
+  </si>
+  <si>
+    <t>按烧烤、火锅、炒菜、早茶等分类；比较人均、六人总价、包间、排队和招牌菜。</t>
+  </si>
+  <si>
+    <t>适合安排</t>
+  </si>
+  <si>
+    <t>人均价格</t>
+  </si>
+  <si>
+    <t>六人预计总价</t>
+  </si>
+  <si>
+    <t>招牌菜</t>
+  </si>
+  <si>
+    <t>包间</t>
+  </si>
+  <si>
+    <t>六人适合度</t>
+  </si>
+  <si>
+    <t>排队情况</t>
+  </si>
+  <si>
+    <t>营业时间</t>
+  </si>
+  <si>
+    <t>预约要求</t>
+  </si>
+  <si>
+    <t>老城 / 瘦西湖周边待选</t>
+  </si>
+  <si>
+    <t>早餐时段待核实</t>
+  </si>
+  <si>
+    <t>核对能否提前排号或预约</t>
+  </si>
+  <si>
+    <t>流程示例，等待餐厅链接核实</t>
+  </si>
+  <si>
+    <t>密室候选</t>
+  </si>
+  <si>
+    <t>按主题和玩法分类；比较微恐/中恐、难度、规模、人数、价格、NPC 和预约规则。</t>
+  </si>
+  <si>
+    <t>主题名称</t>
+  </si>
+  <si>
+    <t>单人价格</t>
+  </si>
+  <si>
+    <t>恐怖程度</t>
+  </si>
+  <si>
+    <t>难度</t>
+  </si>
+  <si>
+    <t>玩法类型</t>
+  </si>
+  <si>
+    <t>场地规模</t>
+  </si>
+  <si>
+    <t>房间数量</t>
+  </si>
+  <si>
+    <t>推荐人数</t>
+  </si>
+  <si>
+    <t>最少人数</t>
+  </si>
+  <si>
+    <t>最多人数</t>
+  </si>
+  <si>
+    <t>六人独立开场</t>
+  </si>
+  <si>
+    <t>时长</t>
+  </si>
+  <si>
+    <t>NPC/真人互动</t>
+  </si>
+  <si>
+    <t>体力消耗</t>
+  </si>
+  <si>
+    <t>换装</t>
+  </si>
+  <si>
+    <t>六人密室主题待选</t>
+  </si>
+  <si>
+    <t>扬州市区待选</t>
+  </si>
+  <si>
+    <t>团队确认</t>
+  </si>
+  <si>
+    <t>中等优先</t>
+  </si>
+  <si>
+    <t>6 人</t>
+  </si>
+  <si>
     <t>约 2 小时</t>
   </si>
   <si>
-    <t>适合把晚餐、散步和采购伴手礼放在一起</t>
-  </si>
-  <si>
-    <t>热门时段可能拥挤，网红商户仍需单独筛选</t>
-  </si>
-  <si>
-    <t>place-3380833f-f6d0-41eb-9718-7edde5088a6d</t>
-  </si>
-  <si>
-    <t>攻略</t>
-  </si>
-  <si>
-    <t>扬州美食攻略｜10大bi吃</t>
-  </si>
-  <si>
-    <t>待核实</t>
-  </si>
-  <si>
-    <t>扬州美食；扬州旅游攻略；扬州必吃；江浙沪周边游</t>
-  </si>
-  <si>
-    <t>涵盖经典扬州美食</t>
-  </si>
-  <si>
-    <t>未包含所有美食，评论区可补充</t>
-  </si>
-  <si>
-    <t>价格或预约等动态信息仍需核实</t>
-  </si>
-  <si>
-    <t>待比较</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>http://xhslink.com/o/5HrEeOTXkGr</t>
-  </si>
-  <si>
-    <t>place-b34f514c-cc18-49a3-873b-8651853e07b9</t>
-  </si>
-  <si>
-    <t>扬州市</t>
-  </si>
-  <si>
-    <t>江苏省</t>
-  </si>
-  <si>
-    <t>历史文化；美食；园林；运河</t>
-  </si>
-  <si>
-    <t>美食之都</t>
-  </si>
-  <si>
-    <t>部分信息待核实</t>
-  </si>
-  <si>
-    <t>住宿；活动；餐饮具体信息；主要风险</t>
-  </si>
-  <si>
-    <t>https://zh.wikipedia.org/wiki/%E6%89%AC%E5%B7%9E%E5%B8%82</t>
-  </si>
-  <si>
-    <t>place-005</t>
-  </si>
-  <si>
-    <t>老城精品民宿候选</t>
-  </si>
-  <si>
-    <t>东关街周边</t>
-  </si>
-  <si>
-    <t>¥520</t>
-  </si>
-  <si>
-    <t>目标至少 3 个独立睡眠空间</t>
-  </si>
-  <si>
-    <t>靠近老城景点，可减少第一天晚间交通</t>
-  </si>
-  <si>
-    <t>仅为占位候选，房型、噪音和停车情况都要看真实链接</t>
-  </si>
-  <si>
-    <t>价格或预约等动态信息仍需核实；详细地址；6 人容量；户型；床位 / 床型；卫浴；烧烤；取消政策</t>
-  </si>
-  <si>
-    <t>place-007</t>
-  </si>
-  <si>
-    <t>团队密室候选</t>
-  </si>
-  <si>
-    <t>扬州市区</t>
-  </si>
-  <si>
-    <t>待团队投递</t>
-  </si>
-  <si>
-    <t>6 人；约 2 小时；中等优先；团队确认</t>
-  </si>
-  <si>
-    <t>可作为晚间或雨天的团队活动</t>
-  </si>
-  <si>
-    <t>暂无真实商户资料，需要补充密室链接后再比较</t>
-  </si>
-  <si>
-    <t>价格或预约等动态信息仍需核实；价格；营业时间；预约要求；取消政策</t>
-  </si>
-  <si>
-    <t>place-008</t>
-  </si>
-  <si>
-    <t>扬州两日慢游示例资料</t>
-  </si>
-  <si>
-    <t>不适用</t>
-  </si>
-  <si>
-    <t>路线框架；流程示例</t>
-  </si>
-  <si>
-    <t>提供了园林、老城和运河三条内容线索</t>
-  </si>
-  <si>
-    <t>并非真实攻略文章，正式使用时应由团队链接替换</t>
-  </si>
-  <si>
-    <t>https://example.com/yangzhou-guide</t>
-  </si>
-  <si>
-    <t>链接汇总</t>
-  </si>
-  <si>
-    <t>每一条团队链接的完整台账；读取失败也会保留，不会静默丢失。</t>
-  </si>
-  <si>
-    <t>提交时间</t>
-  </si>
-  <si>
-    <t>提交人</t>
-  </si>
-  <si>
-    <t>页面标题</t>
-  </si>
-  <si>
-    <t>自动分类</t>
-  </si>
-  <si>
-    <t>读取结果</t>
-  </si>
-  <si>
-    <t>整理结果</t>
-  </si>
-  <si>
-    <t>处理状态</t>
-  </si>
-  <si>
-    <t>已提取信息</t>
-  </si>
-  <si>
-    <t>AI摘要</t>
-  </si>
-  <si>
-    <t>分析模型</t>
-  </si>
-  <si>
-    <t>错误原因</t>
-  </si>
-  <si>
-    <t>link-0c57f71b3b10</t>
-  </si>
-  <si>
-    <t>2026-07-20T12:48:03.252Z</t>
-  </si>
-  <si>
-    <t>ykh</t>
-  </si>
-  <si>
-    <t>扬州美食攻略｜10大bi吃，有人同意吗？ - 小红书</t>
-  </si>
-  <si>
-    <t>成功读取</t>
-  </si>
-  <si>
-    <t>已整理</t>
-  </si>
-  <si>
-    <t>已写入Excel</t>
-  </si>
-  <si>
-    <t>页面标题；内容分类；核心摘要</t>
-  </si>
-  <si>
-    <t>扬州10大必吃美食：扬州炒饭、三丁包、蟹粉狮子头、大煮干丝、文思豆腐、翡翠烧麦、千层油糕、扬州灌汤包、高邮咸鸭蛋、盐水鹅。</t>
-  </si>
-  <si>
-    <t>DeepSeek · deepseek-v4-flash</t>
-  </si>
-  <si>
-    <t>link-df4b1ba42b06</t>
-  </si>
-  <si>
-    <t>2026-07-20T12:33:13.051Z</t>
-  </si>
-  <si>
-    <t>Codex 流程测试</t>
-  </si>
-  <si>
-    <t>扬州市 - 维基百科，自由的百科全书</t>
-  </si>
-  <si>
-    <t>扬州是首批国家历史文化名城；拥有瘦西湖、个园等景点；淮扬菜发源地</t>
-  </si>
-  <si>
-    <t>住宿；活动；餐饮具体信息</t>
-  </si>
-  <si>
-    <t>扬州是江苏省地级市，国家历史文化名城，以淮扬菜、园林和运河文化闻名，适合周末旅行。</t>
-  </si>
-  <si>
-    <t>验证 DeepSeek 解析并写入 Excel；测试完成后保留为示例资料</t>
-  </si>
-  <si>
-    <t>seed-guide-001</t>
-  </si>
-  <si>
-    <t>2026-07-20T02:00:00.000Z</t>
-  </si>
-  <si>
-    <t>系统示例</t>
-  </si>
-  <si>
-    <t>示例资料：以瘦西湖、老城园林和运河博物馆串联两天路线。</t>
-  </si>
-  <si>
-    <t>演示分析</t>
-  </si>
-  <si>
-    <t>用于演示完整流程，可在正式收集后删除</t>
-  </si>
-  <si>
-    <t>处理报告</t>
-  </si>
-  <si>
-    <t>快速查看哪些链接已成功整理、哪些未整理，以及缺失了什么。</t>
-  </si>
-  <si>
-    <t>结果说明</t>
-  </si>
-  <si>
-    <t>更新时间</t>
-  </si>
-  <si>
-    <t>已生成候选资料并写入 Excel</t>
-  </si>
-  <si>
-    <t>2026-07-20T12:48:06.535Z</t>
-  </si>
-  <si>
-    <t>已整理；仍有 3 项待核实</t>
-  </si>
-  <si>
-    <t>2026-07-20T13:17:54.301Z</t>
-  </si>
-  <si>
-    <t>2026-07-20T02:02:00.000Z</t>
-  </si>
-  <si>
-    <t>住宿候选</t>
-  </si>
-  <si>
-    <t>民宿完整明细：价格、位置、户型、床位、烧烤、费用和取消政策；黄色列可直接修改。</t>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <t>地段特点</t>
-  </si>
-  <si>
-    <t>核心景点距离</t>
-  </si>
-  <si>
-    <t>每晚价格</t>
-  </si>
-  <si>
-    <t>额外费用</t>
-  </si>
-  <si>
-    <t>押金</t>
-  </si>
-  <si>
-    <t>户型</t>
-  </si>
-  <si>
-    <t>房间</t>
-  </si>
-  <si>
-    <t>床位</t>
-  </si>
-  <si>
-    <t>床型</t>
-  </si>
-  <si>
-    <t>卫浴</t>
-  </si>
-  <si>
-    <t>环境特点</t>
-  </si>
-  <si>
-    <t>是否整租</t>
-  </si>
-  <si>
-    <t>厨房</t>
-  </si>
-  <si>
-    <t>烧烤设备/费用</t>
-  </si>
-  <si>
-    <t>停车</t>
-  </si>
-  <si>
-    <t>入住时间</t>
-  </si>
-  <si>
-    <t>退房时间</t>
-  </si>
-  <si>
-    <t>取消政策</t>
-  </si>
-  <si>
-    <t>预订要求</t>
-  </si>
-  <si>
-    <t>优点</t>
-  </si>
-  <si>
-    <t>缺点</t>
-  </si>
-  <si>
-    <t>推荐分</t>
-  </si>
-  <si>
-    <t>证据摘要</t>
-  </si>
-  <si>
-    <t>投票详情</t>
-  </si>
-  <si>
-    <t>数据状态</t>
-  </si>
-  <si>
-    <t>东关街周边（具体门牌待真实链接）</t>
-  </si>
-  <si>
-    <t>日期和房源确认后计算</t>
-  </si>
-  <si>
-    <t>目标 6 人，实际容量待核实</t>
-  </si>
-  <si>
-    <t>床型与床数待核实</t>
-  </si>
-  <si>
-    <t>环境好、安静、公共空间充足</t>
-  </si>
-  <si>
-    <t>整租优先，待核实</t>
-  </si>
-  <si>
-    <t>希望可用，待核实</t>
-  </si>
-  <si>
-    <t>必须确认允许，当前未知</t>
-  </si>
-  <si>
-    <t>设备、炭火和清洁费待核实</t>
-  </si>
-  <si>
-    <t>不强求含早，周边早餐需方便</t>
-  </si>
-  <si>
-    <t>老城步行 / 打车便利优先</t>
-  </si>
-  <si>
-    <t>周五晚，具体时间待核实</t>
-  </si>
-  <si>
-    <t>周日，具体时间待核实</t>
-  </si>
-  <si>
-    <t>等待团队提交真实民宿链接</t>
-  </si>
-  <si>
-    <t>纯示例住宿，等待团队提交真实民宿</t>
-  </si>
-  <si>
-    <t>活动候选</t>
-  </si>
-  <si>
-    <t>密室和景点完整明细：人数、价格、时长、难度、预约与取消政策；黄色列可直接修改。</t>
-  </si>
-  <si>
-    <t>活动类型</t>
-  </si>
-  <si>
-    <t>价格</t>
-  </si>
-  <si>
-    <t>时长</t>
-  </si>
-  <si>
-    <t>难度</t>
-  </si>
-  <si>
-    <t>恐怖程度</t>
-  </si>
-  <si>
-    <t>营业时间</t>
-  </si>
-  <si>
-    <t>预约要求</t>
+    <t>通常需预约，具体规则待真实链接</t>
+  </si>
+  <si>
+    <t>空位候选，等待真实密室链接</t>
+  </si>
+  <si>
+    <t>室内休闲</t>
+  </si>
+  <si>
+    <t>按汗蒸、桑拿、洗浴、温泉等分类；比较套餐、设施、过夜、餐食和使用限制。</t>
+  </si>
+  <si>
+    <t>人均/套餐价格</t>
+  </si>
+  <si>
+    <t>包含设施</t>
+  </si>
+  <si>
+    <t>套餐内容</t>
+  </si>
+  <si>
+    <t>能否过夜</t>
+  </si>
+  <si>
+    <t>是否含餐</t>
+  </si>
+  <si>
+    <t>休息区域</t>
+  </si>
+  <si>
+    <t>独立房间</t>
+  </si>
+  <si>
+    <t>男女分区</t>
+  </si>
+  <si>
+    <t>使用限制</t>
+  </si>
+  <si>
+    <t>景点户外</t>
+  </si>
+  <si>
+    <t>园林、博物馆、历史街区和户外项目；当前优先确认具体地点、票价、开放时间与天气影响。</t>
+  </si>
+  <si>
+    <t>票价</t>
+  </si>
+  <si>
+    <t>票价说明</t>
+  </si>
+  <si>
+    <t>建议时长</t>
+  </si>
+  <si>
+    <t>室内/室外</t>
+  </si>
+  <si>
+    <t>天气影响</t>
+  </si>
+  <si>
+    <t>核心看点</t>
+  </si>
+  <si>
+    <t>注意事项</t>
   </si>
   <si>
     <t>流程示例，等待真实链接核实</t>
@@ -1188,54 +1373,6 @@
     <t>流程示例，等待官方信息核实</t>
   </si>
   <si>
-    <t>扬州市区待选</t>
-  </si>
-  <si>
-    <t>6 人</t>
-  </si>
-  <si>
-    <t>中等优先</t>
-  </si>
-  <si>
-    <t>团队确认</t>
-  </si>
-  <si>
-    <t>通常需预约，具体规则待真实链接</t>
-  </si>
-  <si>
-    <t>空位候选，等待真实密室链接</t>
-  </si>
-  <si>
-    <t>餐饮候选</t>
-  </si>
-  <si>
-    <t>餐厅完整明细：人均、位置、营业时间、适合安排和预约要求；黄色列可直接修改。</t>
-  </si>
-  <si>
-    <t>适合安排</t>
-  </si>
-  <si>
-    <t>人均价格</t>
-  </si>
-  <si>
-    <t>推荐菜/特点</t>
-  </si>
-  <si>
-    <t>老城 / 瘦西湖周边待选</t>
-  </si>
-  <si>
-    <t>早餐时段待核实</t>
-  </si>
-  <si>
-    <t>核对能否提前排号或预约</t>
-  </si>
-  <si>
-    <t>早茶；建议早到；门店待选</t>
-  </si>
-  <si>
-    <t>流程示例，等待餐厅链接核实</t>
-  </si>
-  <si>
     <t>攻略文章</t>
   </si>
   <si>
@@ -1251,9 +1388,6 @@
     <t>避坑信息</t>
   </si>
   <si>
-    <t>交通建议</t>
-  </si>
-  <si>
     <t>partial</t>
   </si>
   <si>
@@ -1275,9 +1409,6 @@
     <t>预计费用/人</t>
   </si>
   <si>
-    <t>注意事项</t>
-  </si>
-  <si>
     <t>来源ID</t>
   </si>
   <si>
@@ -1347,10 +1478,19 @@
     <t>两顿都纳入预订清单</t>
   </si>
   <si>
+    <t>分类体系</t>
+  </si>
+  <si>
+    <t>住宿 / 餐饮 / 密室 / 休闲娱乐 / 景点 / 攻略</t>
+  </si>
+  <si>
+    <t>每类使用不同的提取字段与完整度标准</t>
+  </si>
+  <si>
     <t>团队活动</t>
   </si>
   <si>
-    <t>密室或同类活动</t>
+    <t>密室、汗蒸、桑拿、洗浴或同类活动</t>
   </si>
   <si>
     <t>AI 分析模型</t>
@@ -1411,6 +1551,15 @@
   </si>
   <si>
     <t>含住宿、活动、餐饮、景点和攻略</t>
+  </si>
+  <si>
+    <t>分类明细</t>
+  </si>
+  <si>
+    <t>住宿 1 · 餐饮 1 · 密室 1 · 休闲娱乐 0 · 景点 4 · 攻略 3</t>
+  </si>
+  <si>
+    <t>查看对应分类工作表</t>
   </si>
   <si>
     <t>已入选候选</t>
@@ -1442,7 +1591,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1545,8 +1694,13 @@
       <sz val="9"/>
       <name val="PingFang SC"/>
     </font>
+    <font>
+      <color rgb="5F553E"/>
+      <sz val="9"/>
+      <name val="PingFang SC"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1598,6 +1752,11 @@
         <fgColor rgb="F7F1E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1629,7 +1788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1711,6 +1870,9 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1727,11 +1889,17 @@
     <xf numFmtId="165" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3280,6 +3448,857 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="18" style="17" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="36" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="J4" s="31">
+        <v>1</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="L4" s="24">
+        <v>0</v>
+      </c>
+      <c r="M4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="24">
+        <v>0</v>
+      </c>
+      <c r="O4" s="24"/>
+      <c r="P4" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="R4" s="28"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="J5" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0</v>
+      </c>
+      <c r="O5" s="14"/>
+      <c r="P5" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q5" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="R5" s="28"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="J6" s="31">
+        <v>1</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24"/>
+      <c r="P6" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q6" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="R6" s="28"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="U6" s="24" t="s">
+        <v>454</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:U6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="P4:P6">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Q4:Q6">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="24">
+        <v>30</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="24">
+        <v>80</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="24">
+        <v>0</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="14">
+        <v>120</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="24">
+        <v>40</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="14">
+        <v>150</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="24">
+        <v>100</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="14">
+        <v>0</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="I14" s="24">
+        <v>60</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:M14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L扬州团队旅行攻略&amp;R第 &amp;P / &amp;N 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
@@ -3290,28 +4309,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>419</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="A2" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -3509,12 +4528,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -3522,28 +4541,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>421</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="A2" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>422</v>
+        <v>465</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>423</v>
+        <v>466</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>424</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3554,18 +4573,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>425</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>426</v>
+        <v>469</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>427</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3576,7 +4595,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3587,40 +4606,40 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>429</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>430</v>
+        <v>473</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>432</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>434</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>437</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3628,47 +4647,58 @@
         <v>91</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>130</v>
+        <v>484</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>441</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>309</v>
+        <v>130</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>443</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>444</v>
+        <v>488</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>445</v>
+        <v>319</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>446</v>
+        <v>489</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C14"/>
+  <autoFilter ref="A3:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -3681,12 +4711,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -3694,120 +4724,131 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>447</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="A1" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
+      <c r="A2" s="33" t="s">
+        <v>494</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>424</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="B5" s="14">
         <v>3</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>455</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>456</v>
+        <v>502</v>
       </c>
       <c r="B6" s="24">
         <v>3</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>459</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>460</v>
+        <v>506</v>
       </c>
       <c r="B8" s="24">
         <v>10</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>461</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="B9" s="14">
-        <v>5</v>
+        <v>508</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>509</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>464</v>
+        <v>511</v>
       </c>
       <c r="B10" s="24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>466</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>467</v>
+        <v>513</v>
+      </c>
+      <c r="B11" s="14">
+        <v>6</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>468</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C11"/>
+  <autoFilter ref="A3:C12"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -3826,27 +4867,29 @@
     <tabColor rgb="D9703E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="13" style="17" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="12" style="18" customWidth="1"/>
-    <col min="12" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
-    <col min="18" max="18" width="36" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="13" style="17" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="13" max="13" width="12" style="18" customWidth="1"/>
+    <col min="14" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="28" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>191</v>
       </c>
@@ -3867,8 +4910,11 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="19"/>
       <c r="R1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>192</v>
       </c>
@@ -3889,8 +4935,11 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -3915,19 +4964,19 @@
       <c r="H3" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>200</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="22" t="s">
         <v>202</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="23" t="s">
         <v>204</v>
       </c>
       <c r="N3" s="21" t="s">
@@ -3945,550 +4994,629 @@
       <c r="R3" s="21" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F4" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="G4" s="24" t="s">
-        <v>215</v>
-      </c>
       <c r="H4" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="I4" s="25">
-        <v>0.2857142857142857</v>
+        <v>99</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>218</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="K4" s="26">
+        <v>219</v>
+      </c>
+      <c r="K4" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="M4" s="26">
         <v>4.8</v>
-      </c>
-      <c r="L4" s="24">
-        <v>0</v>
-      </c>
-      <c r="M4" s="24">
-        <v>0</v>
       </c>
       <c r="N4" s="24">
         <v>0</v>
       </c>
-      <c r="O4" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="P4" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="24"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O4" s="24">
+        <v>0</v>
+      </c>
+      <c r="P4" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="S4" s="28"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>221</v>
-      </c>
       <c r="E5" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>223</v>
+        <v>141</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="I5" s="25">
-        <v>0.42857142857142855</v>
+        <v>226</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K5" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="M5" s="30">
         <v>4.7</v>
-      </c>
-      <c r="L5" s="14">
-        <v>0</v>
-      </c>
-      <c r="M5" s="14">
-        <v>0</v>
       </c>
       <c r="N5" s="14">
         <v>0</v>
       </c>
-      <c r="O5" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="P5" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="14"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O5" s="14">
+        <v>0</v>
+      </c>
+      <c r="P5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="R5" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="S5" s="28"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D6" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>213</v>
-      </c>
       <c r="F6" s="24" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="I6" s="25">
-        <v>0.2857142857142857</v>
+        <v>99</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>232</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="K6" s="26">
+        <v>233</v>
+      </c>
+      <c r="K6" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="M6" s="26">
         <v>4.6</v>
-      </c>
-      <c r="L6" s="24">
-        <v>0</v>
-      </c>
-      <c r="M6" s="24">
-        <v>0</v>
       </c>
       <c r="N6" s="24">
         <v>0</v>
       </c>
-      <c r="O6" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="P6" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="24"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O6" s="24">
+        <v>0</v>
+      </c>
+      <c r="P6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="R6" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="S6" s="28"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>136</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F7" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>236</v>
-      </c>
       <c r="H7" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="I7" s="30">
-        <v>0.8</v>
+        <v>239</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>240</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K7" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="M7" s="30">
         <v>4.4</v>
-      </c>
-      <c r="L7" s="14">
-        <v>0</v>
-      </c>
-      <c r="M7" s="14">
-        <v>0</v>
       </c>
       <c r="N7" s="14">
         <v>0</v>
       </c>
-      <c r="O7" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="P7" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="14"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="S7" s="28"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="I8" s="25">
-        <v>0.42857142857142855</v>
+        <v>99</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>247</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="K8" s="26">
+        <v>248</v>
+      </c>
+      <c r="K8" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="M8" s="26">
         <v>4.3</v>
-      </c>
-      <c r="L8" s="24">
-        <v>0</v>
-      </c>
-      <c r="M8" s="24">
-        <v>0</v>
       </c>
       <c r="N8" s="24">
         <v>0</v>
       </c>
-      <c r="O8" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="P8" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="24"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O8" s="24">
+        <v>0</v>
+      </c>
+      <c r="P8" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="R8" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="S8" s="28"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D9" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>248</v>
-      </c>
       <c r="F9" s="14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G9" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I9" s="30">
+      <c r="I9" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="K9" s="31">
         <v>1</v>
       </c>
-      <c r="J9" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="K9" s="29">
+      <c r="L9" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="M9" s="30">
         <v>4.5</v>
-      </c>
-      <c r="L9" s="14">
-        <v>0</v>
-      </c>
-      <c r="M9" s="14">
-        <v>0</v>
       </c>
       <c r="N9" s="14">
         <v>0</v>
       </c>
-      <c r="O9" s="27" t="s">
+      <c r="O9" s="14">
+        <v>0</v>
+      </c>
+      <c r="P9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="R9" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="S9" s="28"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="F10" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="P9" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="14" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>259</v>
-      </c>
       <c r="G10" s="24" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="I10" s="30">
+        <v>250</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="31">
         <v>0.75</v>
       </c>
-      <c r="J10" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="K10" s="26">
+      <c r="L10" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="M10" s="26">
         <v>4.5</v>
-      </c>
-      <c r="L10" s="24">
-        <v>0</v>
-      </c>
-      <c r="M10" s="24">
-        <v>0</v>
       </c>
       <c r="N10" s="24">
         <v>0</v>
       </c>
-      <c r="O10" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P10" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O10" s="24">
+        <v>0</v>
+      </c>
+      <c r="P10" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="R10" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="S10" s="28"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="I11" s="25">
+        <v>81</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="K11" s="25">
         <v>0.2222222222222222</v>
       </c>
-      <c r="J11" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="K11" s="29">
+      <c r="L11" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="M11" s="30">
         <v>4.1</v>
-      </c>
-      <c r="L11" s="14">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14">
-        <v>0</v>
       </c>
       <c r="N11" s="14">
         <v>0</v>
       </c>
-      <c r="O11" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P11" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="14"/>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O11" s="14">
+        <v>0</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="R11" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="S11" s="28"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="I12" s="25">
-        <v>0.42857142857142855</v>
+        <v>286</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>287</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="K12" s="26">
+        <v>288</v>
+      </c>
+      <c r="K12" s="29">
+        <v>0.6</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="M12" s="26">
         <v>3.8</v>
-      </c>
-      <c r="L12" s="24">
-        <v>0</v>
-      </c>
-      <c r="M12" s="24">
-        <v>0</v>
       </c>
       <c r="N12" s="24">
         <v>0</v>
       </c>
-      <c r="O12" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P12" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="24"/>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O12" s="24">
+        <v>0</v>
+      </c>
+      <c r="P12" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="R12" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="S12" s="28"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>282</v>
-      </c>
       <c r="F13" s="14" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="I13" s="30">
+        <v>250</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="K13" s="31">
         <v>1</v>
       </c>
-      <c r="J13" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="K13" s="29">
+      <c r="L13" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="M13" s="30">
         <v>3.5</v>
-      </c>
-      <c r="L13" s="14">
-        <v>0</v>
-      </c>
-      <c r="M13" s="14">
-        <v>0</v>
       </c>
       <c r="N13" s="14">
         <v>0</v>
       </c>
-      <c r="O13" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P13" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="14" t="s">
-        <v>286</v>
+      <c r="O13" s="14">
+        <v>0</v>
+      </c>
+      <c r="P13" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="R13" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="S13" s="28"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R13"/>
+  <autoFilter ref="A3:U13"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="O10:O13">
+    <dataValidation type="list" sqref="Q10:Q13">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O4:O13">
+    <dataValidation type="list" sqref="Q4:Q13">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P10:P13">
+    <dataValidation type="list" sqref="R10:R13">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P4:P13">
+    <dataValidation type="list" sqref="R4:R13">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4505,7 +5633,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4513,236 +5641,251 @@
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="9" width="16" customWidth="1"/>
-    <col min="10" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="10" width="16" customWidth="1"/>
+    <col min="11" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E3" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>291</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="H6" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="I6" s="24" t="s">
         <v>315</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="J6" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="M5" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14" t="s">
+      <c r="K6" s="24" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>252</v>
-      </c>
       <c r="L6" s="24" t="s">
-        <v>321</v>
+        <v>257</v>
       </c>
       <c r="M6" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24" t="s">
-        <v>323</v>
+        <v>331</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O6"/>
+  <autoFilter ref="A3:P6"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4757,202 +5900,217 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="6" width="16" customWidth="1"/>
-    <col min="7" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="7" width="16" customWidth="1"/>
+    <col min="8" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="36" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>193</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>293</v>
+        <v>194</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>299</v>
+        <v>203</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>209</v>
+        <v>309</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G4" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>328</v>
       </c>
-      <c r="H4" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="G5" s="14" t="s">
+      <c r="B6" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="C6" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="G6" s="24" t="s">
         <v>315</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>328</v>
-      </c>
       <c r="H6" s="24" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24" t="s">
-        <v>286</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="K6" s="24"/>
       <c r="L6" s="24" t="s">
-        <v>332</v>
+        <v>297</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L6"/>
+  <autoFilter ref="A3:M6"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4967,47 +6125,50 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AR4"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="16" style="33" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16" style="34" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="30" customWidth="1"/>
-    <col min="25" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="30" customWidth="1"/>
-    <col min="28" max="28" width="18" customWidth="1"/>
-    <col min="29" max="29" width="16" customWidth="1"/>
-    <col min="30" max="31" width="30" customWidth="1"/>
-    <col min="32" max="32" width="16" style="18" customWidth="1"/>
-    <col min="33" max="33" width="18" style="17" customWidth="1"/>
-    <col min="34" max="35" width="30" customWidth="1"/>
-    <col min="36" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="30" customWidth="1"/>
-    <col min="43" max="43" width="36" customWidth="1"/>
-    <col min="44" max="44" width="16" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="30" customWidth="1"/>
+    <col min="27" max="28" width="16" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="16" customWidth="1"/>
+    <col min="32" max="33" width="30" customWidth="1"/>
+    <col min="34" max="34" width="16" style="18" customWidth="1"/>
+    <col min="35" max="35" width="18" style="17" customWidth="1"/>
+    <col min="36" max="37" width="30" customWidth="1"/>
+    <col min="38" max="43" width="18" customWidth="1"/>
+    <col min="44" max="44" width="30" customWidth="1"/>
+    <col min="45" max="45" width="18" customWidth="1"/>
+    <col min="46" max="46" width="36" customWidth="1"/>
+    <col min="47" max="47" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -5052,10 +6213,13 @@
       <c r="AP1" s="19"/>
       <c r="AQ1" s="19"/>
       <c r="AR1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS1" s="19"/>
+      <c r="AT1" s="19"/>
+      <c r="AU1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -5100,130 +6264,133 @@
       <c r="AP2" s="20"/>
       <c r="AQ2" s="20"/>
       <c r="AR2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>335</v>
-      </c>
       <c r="D3" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>338</v>
+      <c r="G3" s="21" t="s">
+        <v>346</v>
       </c>
       <c r="H3" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="I3" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>340</v>
-      </c>
       <c r="K3" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>342</v>
-      </c>
       <c r="N3" s="21" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="T3" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="V3" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="V3" s="21" t="s">
+      <c r="W3" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X3" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="W3" s="21" t="s">
-        <v>350</v>
-      </c>
-      <c r="X3" s="21" t="s">
+      <c r="Y3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="Z3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="Y3" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>352</v>
-      </c>
       <c r="AA3" s="21" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AC3" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="AE3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="AD3" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="AE3" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="AF3" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="AG3" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="AH3" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI3" s="21" t="s">
-        <v>358</v>
+      <c r="AF3" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH3" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="AI3" s="22" t="s">
+        <v>202</v>
       </c>
       <c r="AJ3" s="21" t="s">
         <v>203</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>204</v>
+        <v>368</v>
       </c>
       <c r="AL3" s="21" t="s">
         <v>205</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>359</v>
+        <v>206</v>
       </c>
       <c r="AN3" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>207</v>
+        <v>369</v>
       </c>
       <c r="AP3" s="21" t="s">
         <v>208</v>
@@ -5232,148 +6399,164 @@
         <v>209</v>
       </c>
       <c r="AR3" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="AS3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AT3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="AU3" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="G4" s="35">
+        <v>270</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" s="37">
         <v>520</v>
       </c>
-      <c r="H4" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>248</v>
+      <c r="J4" s="36" t="s">
+        <v>372</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>363</v>
+        <v>253</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>364</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="P4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>366</v>
+        <v>253</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="N4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="R4" s="36" t="s">
+        <v>253</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="V4" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="W4" s="24" t="s">
-        <v>248</v>
+        <v>377</v>
+      </c>
+      <c r="V4" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="W4" s="36" t="s">
+        <v>379</v>
       </c>
       <c r="X4" s="24" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>372</v>
+        <v>253</v>
       </c>
       <c r="Z4" s="24" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AA4" s="24" t="s">
-        <v>248</v>
+        <v>382</v>
       </c>
       <c r="AB4" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC4" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="AD4" s="24" t="s">
+        <v>384</v>
+      </c>
+      <c r="AE4" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="AD4" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="AE4" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="AF4" s="26">
+      <c r="AF4" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG4" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="AH4" s="26">
         <v>4.1</v>
       </c>
-      <c r="AG4" s="25">
+      <c r="AI4" s="25">
         <v>0.2222222222222222</v>
       </c>
-      <c r="AH4" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="AI4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="AJ4" s="24">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="24">
-        <v>0</v>
+      <c r="AJ4" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="AK4" s="24" t="s">
+        <v>253</v>
       </c>
       <c r="AL4" s="24">
         <v>0</v>
       </c>
-      <c r="AM4" s="24"/>
-      <c r="AN4" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="AO4" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="24"/>
-      <c r="AR4" s="24" t="s">
-        <v>375</v>
+      <c r="AM4" s="24">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="24">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="AQ4" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="24"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AR4"/>
+  <autoFilter ref="A3:AU4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AR1"/>
-    <mergeCell ref="A2:AR2"/>
+    <mergeCell ref="A1:AU1"/>
+    <mergeCell ref="A2:AU2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="AN4">
+    <dataValidation type="list" sqref="AP4">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AO4">
+    <dataValidation type="list" sqref="AQ4">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5390,33 +6573,37 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" style="33" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="16" style="34" customWidth="1"/>
+    <col min="9" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="16" width="30" customWidth="1"/>
-    <col min="17" max="17" width="16" style="18" customWidth="1"/>
-    <col min="18" max="18" width="18" style="17" customWidth="1"/>
-    <col min="19" max="20" width="30" customWidth="1"/>
-    <col min="21" max="26" width="18" customWidth="1"/>
-    <col min="27" max="27" width="30" customWidth="1"/>
-    <col min="28" max="28" width="36" customWidth="1"/>
-    <col min="29" max="29" width="16" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="21" width="30" customWidth="1"/>
+    <col min="22" max="22" width="16" style="18" customWidth="1"/>
+    <col min="23" max="23" width="18" style="17" customWidth="1"/>
+    <col min="24" max="25" width="30" customWidth="1"/>
+    <col min="26" max="31" width="18" customWidth="1"/>
+    <col min="32" max="32" width="30" customWidth="1"/>
+    <col min="33" max="33" width="18" customWidth="1"/>
+    <col min="34" max="34" width="36" customWidth="1"/>
+    <col min="35" max="35" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -5446,10 +6633,16 @@
       <c r="AA1" s="19"/>
       <c r="AB1" s="19"/>
       <c r="AC1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -5479,516 +6672,230 @@
       <c r="AA2" s="20"/>
       <c r="AB2" s="20"/>
       <c r="AC2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>378</v>
-      </c>
       <c r="D3" s="21" t="s">
-        <v>335</v>
+        <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="34" t="s">
-        <v>379</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>380</v>
+      <c r="H3" s="35" t="s">
+        <v>389</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="N3" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="S3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="R3" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="T3" s="21" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="U3" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="V3" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="W3" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="X3" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="V3" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="W3" s="21" t="s">
+      <c r="Y3" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="Z3" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="X3" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="Y3" s="21" t="s">
+      <c r="AA3" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="AB3" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AC3" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="AD3" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="AB3" s="21" t="s">
+      <c r="AE3" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="AC3" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AF3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="AI3" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="35"/>
-      <c r="G4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>215</v>
+        <v>234</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="H4" s="37">
+        <v>80</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>399</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q4" s="26">
-        <v>4.8</v>
-      </c>
-      <c r="R4" s="25">
-        <v>0.2857142857142857</v>
+        <v>253</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>253</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="U4" s="24">
+        <v>240</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="V4" s="26">
+        <v>4.4</v>
+      </c>
+      <c r="W4" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z4" s="24">
         <v>0</v>
       </c>
-      <c r="V4" s="24">
+      <c r="AA4" s="24">
         <v>0</v>
       </c>
-      <c r="W4" s="24">
+      <c r="AB4" s="24">
         <v>0</v>
       </c>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z4" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="F5" s="36">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q5" s="29">
-        <v>4.3</v>
-      </c>
-      <c r="R5" s="25">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="T5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="U5" s="14">
-        <v>0</v>
-      </c>
-      <c r="V5" s="14">
-        <v>0</v>
-      </c>
-      <c r="W5" s="14">
-        <v>0</v>
-      </c>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z5" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="P6" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q6" s="26">
-        <v>4.6</v>
-      </c>
-      <c r="R6" s="25">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S6" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="T6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="U6" s="24">
-        <v>0</v>
-      </c>
-      <c r="V6" s="24">
-        <v>0</v>
-      </c>
-      <c r="W6" s="24">
-        <v>0</v>
-      </c>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z6" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="36">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q7" s="29">
-        <v>4.7</v>
-      </c>
-      <c r="R7" s="25">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="T7" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="U7" s="14">
-        <v>0</v>
-      </c>
-      <c r="V7" s="14">
-        <v>0</v>
-      </c>
-      <c r="W7" s="14">
-        <v>0</v>
-      </c>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z7" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="N8" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="P8" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q8" s="26">
-        <v>3.8</v>
-      </c>
-      <c r="R8" s="25">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="S8" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="T8" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="U8" s="24">
-        <v>0</v>
-      </c>
-      <c r="V8" s="24">
-        <v>0</v>
-      </c>
-      <c r="W8" s="24">
-        <v>0</v>
-      </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z8" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24" t="s">
-        <v>392</v>
+      <c r="AE4" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AC8"/>
+  <autoFilter ref="A3:AI4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A2:AC2"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="A2:AI2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="Y4:Y8">
+    <dataValidation type="list" sqref="AD4">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Z4:Z8">
+    <dataValidation type="list" sqref="AE4">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6005,33 +6912,39 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="16" style="33" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="14" width="30" customWidth="1"/>
-    <col min="15" max="15" width="16" style="18" customWidth="1"/>
-    <col min="16" max="16" width="18" style="17" customWidth="1"/>
-    <col min="17" max="18" width="30" customWidth="1"/>
-    <col min="19" max="24" width="18" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="16" style="34" customWidth="1"/>
+    <col min="9" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="17" width="16" customWidth="1"/>
+    <col min="18" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
     <col min="25" max="25" width="30" customWidth="1"/>
-    <col min="26" max="26" width="36" customWidth="1"/>
-    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="26" max="27" width="16" customWidth="1"/>
+    <col min="28" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="16" style="18" customWidth="1"/>
+    <col min="31" max="31" width="18" style="17" customWidth="1"/>
+    <col min="32" max="33" width="30" customWidth="1"/>
+    <col min="34" max="39" width="18" customWidth="1"/>
+    <col min="40" max="40" width="30" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="36" customWidth="1"/>
+    <col min="43" max="43" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6059,10 +6972,26 @@
       <c r="Y1" s="19"/>
       <c r="Z1" s="19"/>
       <c r="AA1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+      <c r="AP1" s="19"/>
+      <c r="AQ1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6090,178 +7019,286 @@
       <c r="Y2" s="20"/>
       <c r="Z2" s="20"/>
       <c r="AA2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="W3" s="21" t="s">
         <v>395</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="34" t="s">
+      <c r="X3" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="K3" s="21" t="s">
+      <c r="Y3" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="AA3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="S3" s="21" t="s">
+      <c r="AB3" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="AD3" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE3" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF3" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="T3" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="U3" s="21" t="s">
+      <c r="AG3" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="AH3" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="V3" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="W3" s="21" t="s">
+      <c r="AI3" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="Y3" s="21" t="s">
+      <c r="AK3" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="AL3" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="AM3" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="AA3" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AN3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AO3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="AQ3" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>398</v>
-      </c>
-      <c r="G4" s="35">
-        <v>80</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>399</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>400</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="K4" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="H4" s="37"/>
+      <c r="I4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="R4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="S4" s="36" t="s">
+        <v>423</v>
+      </c>
+      <c r="T4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="W4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="AA4" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="L4" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="O4" s="26">
-        <v>4.4</v>
-      </c>
-      <c r="P4" s="30">
-        <v>0.8</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="S4" s="24">
+      <c r="AB4" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="AD4" s="26">
+        <v>3.8</v>
+      </c>
+      <c r="AE4" s="29">
+        <v>0.6</v>
+      </c>
+      <c r="AF4" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="AG4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH4" s="24">
         <v>0</v>
       </c>
-      <c r="T4" s="24">
+      <c r="AI4" s="24">
         <v>0</v>
       </c>
-      <c r="U4" s="24">
+      <c r="AJ4" s="24">
         <v>0</v>
       </c>
-      <c r="V4" s="24"/>
-      <c r="W4" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="X4" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="24" t="s">
-        <v>402</v>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM4" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="24" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AA4"/>
+  <autoFilter ref="A3:AQ4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A1:AQ1"/>
+    <mergeCell ref="A2:AQ2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="W4">
+    <dataValidation type="list" sqref="AL4">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="X4">
+    <dataValidation type="list" sqref="AM4">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6278,24 +7315,40 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="18" style="17" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
-    <col min="18" max="18" width="36" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" style="34" customWidth="1"/>
+    <col min="8" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="13" width="18" customWidth="1"/>
+    <col min="14" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="30" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="25" width="30" customWidth="1"/>
+    <col min="26" max="26" width="16" style="18" customWidth="1"/>
+    <col min="27" max="27" width="18" style="17" customWidth="1"/>
+    <col min="28" max="29" width="30" customWidth="1"/>
+    <col min="30" max="35" width="18" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="18" customWidth="1"/>
+    <col min="38" max="38" width="36" customWidth="1"/>
+    <col min="39" max="39" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6315,10 +7368,30 @@
       <c r="Q1" s="19"/>
       <c r="R1" s="19"/>
       <c r="S1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6338,242 +7411,162 @@
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>405</v>
+        <v>195</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>406</v>
+        <v>194</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>297</v>
+        <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>407</v>
+        <v>345</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>296</v>
+        <v>31</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>428</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>200</v>
+        <v>390</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>429</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>358</v>
+        <v>430</v>
       </c>
       <c r="K3" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="Z3" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="AA3" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB3" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="L3" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="M3" s="21" t="s">
+      <c r="AC3" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="AD3" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="N3" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="O3" s="21" t="s">
+      <c r="AE3" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="AF3" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="AG3" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="AH3" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="AI3" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="S3" s="21" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="I4" s="30">
-        <v>1</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="K4" s="24">
-        <v>0</v>
-      </c>
-      <c r="L4" s="24">
-        <v>0</v>
-      </c>
-      <c r="M4" s="24">
-        <v>0</v>
-      </c>
-      <c r="N4" s="24"/>
-      <c r="O4" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P4" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="I5" s="30">
-        <v>0.75</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="K5" s="14">
-        <v>0</v>
-      </c>
-      <c r="L5" s="14">
-        <v>0</v>
-      </c>
-      <c r="M5" s="14">
-        <v>0</v>
-      </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P5" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="I6" s="30">
-        <v>1</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="K6" s="24">
-        <v>0</v>
-      </c>
-      <c r="L6" s="24">
-        <v>0</v>
-      </c>
-      <c r="M6" s="24">
-        <v>0</v>
-      </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="P6" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="S6" s="24" t="s">
-        <v>410</v>
-      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AK3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AL3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="AM3" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="34:36" x14ac:dyDescent="0.25">
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="39"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S6"/>
+  <autoFilter ref="A3:AM4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:AM1"/>
+    <mergeCell ref="A2:AM2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="O4:O6">
+    <dataValidation type="list" sqref="AH4">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P4:P6">
+    <dataValidation type="list" sqref="AI4">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6590,507 +7583,572 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:AF7"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" style="34" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="16" style="18" customWidth="1"/>
+    <col min="20" max="20" width="18" style="17" customWidth="1"/>
+    <col min="21" max="22" width="30" customWidth="1"/>
+    <col min="23" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="36" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>412</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>60</v>
+        <v>194</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>413</v>
+        <v>345</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
+      <c r="G3" s="35" t="s">
+        <v>439</v>
+      </c>
       <c r="H3" s="21" t="s">
-        <v>65</v>
+        <v>440</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="J3" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="P3" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q3" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="T3" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="24">
-        <v>30</v>
-      </c>
-      <c r="J4" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="G4" s="37"/>
+      <c r="H4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="J4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="P4" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="Q4" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="S4" s="26">
+        <v>4.8</v>
+      </c>
+      <c r="T4" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="W4" s="24">
+        <v>0</v>
+      </c>
+      <c r="X4" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="24">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB4" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="14">
+        <v>243</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" s="37">
         <v>0</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H5" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="J5" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="K5" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="L5" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M5" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="S5" s="30">
+        <v>4.3</v>
+      </c>
+      <c r="T5" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="W5" s="14">
+        <v>0</v>
+      </c>
+      <c r="X5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB5" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="24">
-        <v>80</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="37"/>
+      <c r="H6" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="K6" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="L6" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M6" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="R6" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="S6" s="26">
+        <v>4.6</v>
+      </c>
+      <c r="T6" s="25">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U6" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="V6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="W6" s="24">
+        <v>0</v>
+      </c>
+      <c r="X6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB6" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="14">
+        <v>223</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="37">
         <v>0</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="H7" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="K7" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="L7" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="M7" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="24">
+      <c r="Q7" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="S7" s="30">
+        <v>4.7</v>
+      </c>
+      <c r="T7" s="29">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="W7" s="14">
         <v>0</v>
       </c>
-      <c r="J8" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="I9" s="14">
-        <v>120</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" s="24">
-        <v>40</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="I11" s="14">
-        <v>150</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="I12" s="24">
-        <v>100</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="14">
+      <c r="X7" s="14">
         <v>0</v>
       </c>
-      <c r="J13" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-    </row>
-    <row r="14" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I14" s="24">
-        <v>60</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
+      <c r="Y7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB7" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14" t="s">
+        <v>447</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M14"/>
+  <autoFilter ref="A3:AF7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A2:AF2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="AA4:AA7">
+      <formula1>"待比较,备选,拟定,淘汰"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="AB4:AB7">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>

--- a/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
+++ b/outputs/019f7eda-a998-7660-a73d-e43b3af67965/扬州团队旅行攻略.xlsx
@@ -6,7 +6,7 @@
   <sheets>
     <sheet sheetId="1" name="行程首页" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="候选决策台" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="链接汇总" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="投递汇总" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="处理报告" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="住宿候选" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="美食餐饮" state="visible" r:id="rId9"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="552">
   <si>
     <t>扬州旅行 · 最终方案首页</t>
   </si>
@@ -665,6 +665,12 @@
     <t>人工保护字段</t>
   </si>
   <si>
+    <t>来源类型</t>
+  </si>
+  <si>
+    <t>团队原始诉求</t>
+  </si>
+  <si>
     <t>原始链接</t>
   </si>
   <si>
@@ -698,6 +704,9 @@
     <t>是</t>
   </si>
   <si>
+    <t>链接</t>
+  </si>
+  <si>
     <t>place-004</t>
   </si>
   <si>
@@ -899,6 +908,39 @@
     <t>价格或预约等动态信息仍需核实；单人价格；场地规模；六人独立开场；预约要求</t>
   </si>
   <si>
+    <t>place-74c855d3-c1e8-4eb5-b6fb-0e99a441741a</t>
+  </si>
+  <si>
+    <t>恐怖密室</t>
+  </si>
+  <si>
+    <t>6人中恐密室需求</t>
+  </si>
+  <si>
+    <t>¥200</t>
+  </si>
+  <si>
+    <t>中恐；中等</t>
+  </si>
+  <si>
+    <t>中恐；NPC互动；适合6人；密室；真人互动；需要预约</t>
+  </si>
+  <si>
+    <t>明确预算和恐怖程度</t>
+  </si>
+  <si>
+    <t>未指定具体密室名称</t>
+  </si>
+  <si>
+    <t>具体密室名称；地址；营业时间；取消规则；是否可包场；主题名称；详细地址；场地规模；适合人数；六人独立开场</t>
+  </si>
+  <si>
+    <t>文字</t>
+  </si>
+  <si>
+    <t>团队想找适合6个人一起玩的中恐密室，难度中等，最好有NPC互动，单人预算200元以内，位置在扬州市区，周日上午能预约。</t>
+  </si>
+  <si>
     <t>place-008</t>
   </si>
   <si>
@@ -923,10 +965,10 @@
     <t>https://example.com/yangzhou-guide</t>
   </si>
   <si>
-    <t>链接汇总</t>
-  </si>
-  <si>
-    <t>每一条团队链接的完整台账；读取失败也会保留，不会静默丢失。</t>
+    <t>投递汇总</t>
+  </si>
+  <si>
+    <t>链接和团队文字诉求的完整台账；失败记录也会保留，不会静默丢失。</t>
   </si>
   <si>
     <t>提交时间</t>
@@ -935,7 +977,10 @@
     <t>提交人</t>
   </si>
   <si>
-    <t>页面标题</t>
+    <t>原始内容</t>
+  </si>
+  <si>
+    <t>页面标题 / 需求名称</t>
   </si>
   <si>
     <t>读取结果</t>
@@ -959,6 +1004,42 @@
     <t>错误原因</t>
   </si>
   <si>
+    <t>text-b5a38d52e37e</t>
+  </si>
+  <si>
+    <t>2026-07-22T02:28:31.243Z</t>
+  </si>
+  <si>
+    <t>Codex 文字流程测试</t>
+  </si>
+  <si>
+    <t>团队需求｜团队想找适合6个人一起玩的中恐密室，难度中等，最好有NPC互动，单人预算200元以内…</t>
+  </si>
+  <si>
+    <t>文字已接收</t>
+  </si>
+  <si>
+    <t>已整理</t>
+  </si>
+  <si>
+    <t>已写入Excel</t>
+  </si>
+  <si>
+    <t>适合6人；中恐；难度中等；有NPC互动；单人预算200元以内；位置在扬州市区；周日上午能预约</t>
+  </si>
+  <si>
+    <t>具体密室名称；地址；营业时间；取消规则；是否可包场</t>
+  </si>
+  <si>
+    <t>团队希望找扬州市区的中恐密室，难度中等，有NPC互动，单人预算200元以内，周日上午可预约，适合6人。</t>
+  </si>
+  <si>
+    <t>DeepSeek · deepseek-v4-flash</t>
+  </si>
+  <si>
+    <t>验证文字诉求经 DeepSeek 整理并写入 Excel</t>
+  </si>
+  <si>
     <t>link-0c57f71b3b10</t>
   </si>
   <si>
@@ -974,21 +1055,12 @@
     <t>成功读取</t>
   </si>
   <si>
-    <t>已整理</t>
-  </si>
-  <si>
-    <t>已写入Excel</t>
-  </si>
-  <si>
     <t>页面标题；内容分类；核心摘要</t>
   </si>
   <si>
     <t>扬州10大必吃美食：扬州炒饭、三丁包、蟹粉狮子头、大煮干丝、文思豆腐、翡翠烧麦、千层油糕、扬州灌汤包、高邮咸鸭蛋、盐水鹅。</t>
   </si>
   <si>
-    <t>DeepSeek · deepseek-v4-flash</t>
-  </si>
-  <si>
     <t>link-df4b1ba42b06</t>
   </si>
   <si>
@@ -1034,7 +1106,7 @@
     <t>处理报告</t>
   </si>
   <si>
-    <t>快速查看哪些链接已成功整理、哪些未整理，以及缺失了什么。</t>
+    <t>快速查看哪些投递已成功整理、哪些未整理，以及缺失了什么。</t>
   </si>
   <si>
     <t>结果说明</t>
@@ -1043,6 +1115,12 @@
     <t>更新时间</t>
   </si>
   <si>
+    <t>已整理；仍有 5 项待核实</t>
+  </si>
+  <si>
+    <t>2026-07-22T02:31:56.463Z</t>
+  </si>
+  <si>
     <t>已生成候选资料并写入 Excel</t>
   </si>
   <si>
@@ -1283,6 +1361,30 @@
     <t>换装</t>
   </si>
   <si>
+    <t>中恐</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>周日上午场次</t>
+  </si>
+  <si>
+    <t>周日上午可预约</t>
+  </si>
+  <si>
+    <t>明确预算和恐怖程度；有NPC互动需求；时间明确</t>
+  </si>
+  <si>
+    <t>未指定具体密室名称；未确认是否有6人场次</t>
+  </si>
+  <si>
+    <t>团队文字诉求：适合6人，中恐，难度中等，有NPC互动，单人预算200元以内，扬州市区，周日上午能预约。</t>
+  </si>
+  <si>
+    <t>团队文字需求，具体商户待匹配</t>
+  </si>
+  <si>
     <t>六人密室主题待选</t>
   </si>
   <si>
@@ -1529,19 +1631,19 @@
     <t>6 人，住宿两晚</t>
   </si>
   <si>
-    <t>已收集链接</t>
-  </si>
-  <si>
-    <t>所有链接均保留处理记录</t>
-  </si>
-  <si>
-    <t>已整理链接</t>
+    <t>已收集投递</t>
+  </si>
+  <si>
+    <t>链接 3 · 文字 1</t>
+  </si>
+  <si>
+    <t>已整理投递</t>
   </si>
   <si>
     <t>已形成候选资料并写入分类表</t>
   </si>
   <si>
-    <t>未整理链接</t>
+    <t>未整理投递</t>
   </si>
   <si>
     <t>请在处理报告查看原因并补充信息</t>
@@ -1556,7 +1658,7 @@
     <t>分类明细</t>
   </si>
   <si>
-    <t>住宿 1 · 餐饮 1 · 密室 1 · 休闲娱乐 0 · 景点 4 · 攻略 3</t>
+    <t>住宿 1 · 餐饮 1 · 密室 2 · 休闲娱乐 0 · 景点 4 · 攻略 3</t>
   </si>
   <si>
     <t>查看对应分类工作表</t>
@@ -1577,10 +1679,10 @@
     <t>当前重点</t>
   </si>
   <si>
-    <t>补充真实民宿、两顿早餐和密室链接</t>
-  </si>
-  <si>
-    <t>先核对住宿能否烧烤</t>
+    <t>补充真实民宿、两顿早餐和密室资料</t>
+  </si>
+  <si>
+    <t>可投递链接，也可直接写文字诉求</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3550,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3462,13 +3564,15 @@
     <col min="12" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="30" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="36" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="38" customWidth="1"/>
+    <col min="22" max="22" width="36" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3490,10 +3594,12 @@
       <c r="S1" s="19"/>
       <c r="T1" s="19"/>
       <c r="U1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -3515,13 +3621,15 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>194</v>
@@ -3530,16 +3638,16 @@
         <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>203</v>
@@ -3548,7 +3656,7 @@
         <v>202</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>205</v>
@@ -3560,7 +3668,7 @@
         <v>207</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>208</v>
@@ -3578,42 +3686,48 @@
         <v>212</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E4" s="36" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J4" s="31">
         <v>1</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L4" s="24">
         <v>0</v>
@@ -3626,53 +3740,57 @@
       </c>
       <c r="O4" s="24"/>
       <c r="P4" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R4" s="28"/>
       <c r="S4" s="24"/>
       <c r="T4" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="U4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="W4" s="24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>250</v>
-      </c>
       <c r="E5" s="36" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="J5" s="31">
         <v>0.75</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -3685,53 +3803,57 @@
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R5" s="28"/>
       <c r="S5" s="14"/>
       <c r="T5" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="U5" s="14" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J6" s="31">
         <v>1</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L6" s="24">
         <v>0</v>
@@ -3744,25 +3866,29 @@
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q6" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R6" s="28"/>
       <c r="S6" s="24"/>
       <c r="T6" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="U6" s="24" t="s">
-        <v>454</v>
+        <v>225</v>
+      </c>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="W6" s="24" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:U6"/>
+  <autoFilter ref="A3:W6"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="P4:P6">
@@ -3800,7 +3926,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -3817,7 +3943,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -3846,10 +3972,10 @@
         <v>61</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>31</v>
@@ -3858,16 +3984,16 @@
         <v>65</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>68</v>
@@ -4310,7 +4436,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -4322,7 +4448,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -4542,27 +4668,27 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4573,18 +4699,18 @@
         <v>9</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4595,7 +4721,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4606,40 +4732,40 @@
         <v>2</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4647,54 +4773,54 @@
         <v>91</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -4725,126 +4851,126 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="B5" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>502</v>
+        <v>536</v>
       </c>
       <c r="B6" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="B7" s="14">
         <v>0</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>506</v>
+        <v>540</v>
       </c>
       <c r="B8" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="B10" s="24">
         <v>5</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="B11" s="14">
         <v>6</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>517</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -4867,7 +4993,7 @@
     <tabColor rgb="D9703E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4886,10 +5012,12 @@
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="28" customWidth="1"/>
     <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="21" width="36" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="38" customWidth="1"/>
+    <col min="23" max="23" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>191</v>
       </c>
@@ -4913,8 +5041,10 @@
       <c r="S1" s="19"/>
       <c r="T1" s="19"/>
       <c r="U1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>192</v>
       </c>
@@ -4938,8 +5068,10 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -5003,43 +5135,49 @@
       <c r="U3" s="21" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E4" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="G4" s="24" t="s">
         <v>216</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>214</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>99</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K4" s="25">
         <v>0.42857142857142855</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M4" s="26">
         <v>4.8</v>
@@ -5054,18 +5192,22 @@
         <v>0</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S4" s="28"/>
       <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>99</v>
@@ -5077,28 +5219,28 @@
         <v>142</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>141</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K5" s="29">
         <v>0.5714285714285714</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M5" s="30">
         <v>4.7</v>
@@ -5113,51 +5255,55 @@
         <v>0</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S5" s="28"/>
       <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>110</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H6" s="24" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K6" s="25">
         <v>0.42857142857142855</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M6" s="26">
         <v>4.6</v>
@@ -5172,51 +5318,55 @@
         <v>0</v>
       </c>
       <c r="Q6" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="R6" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S6" s="28"/>
       <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U6" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>136</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F7" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>235</v>
-      </c>
       <c r="H7" s="14" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K7" s="29">
         <v>0.5714285714285714</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M7" s="30">
         <v>4.4</v>
@@ -5231,51 +5381,55 @@
         <v>0</v>
       </c>
       <c r="Q7" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="R7" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S7" s="28"/>
       <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-    </row>
-    <row r="8" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U7" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>99</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K8" s="29">
         <v>0.5714285714285714</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M8" s="26">
         <v>4.3</v>
@@ -5290,51 +5444,55 @@
         <v>0</v>
       </c>
       <c r="Q8" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S8" s="28"/>
       <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U8" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>250</v>
-      </c>
       <c r="I9" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K9" s="31">
         <v>1</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="M9" s="30">
         <v>4.5</v>
@@ -5349,53 +5507,57 @@
         <v>0</v>
       </c>
       <c r="Q9" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R9" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S9" s="28"/>
       <c r="T9" s="14"/>
       <c r="U9" s="14" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F10" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="H10" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="G10" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>250</v>
-      </c>
       <c r="I10" s="24" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K10" s="31">
         <v>0.75</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M10" s="26">
         <v>4.5</v>
@@ -5410,53 +5572,57 @@
         <v>0</v>
       </c>
       <c r="Q10" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S10" s="28"/>
       <c r="T10" s="24"/>
       <c r="U10" s="24" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>81</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K11" s="25">
         <v>0.2222222222222222</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="M11" s="30">
         <v>4.1</v>
@@ -5471,51 +5637,55 @@
         <v>0</v>
       </c>
       <c r="Q11" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R11" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S11" s="28"/>
       <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-    </row>
-    <row r="12" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U11" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K12" s="29">
         <v>0.6</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M12" s="26">
         <v>3.8</v>
@@ -5530,51 +5700,55 @@
         <v>0</v>
       </c>
       <c r="Q12" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S12" s="28"/>
       <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-    </row>
-    <row r="13" ht="34" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U12" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>9</v>
+        <v>286</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="K13" s="31">
-        <v>1</v>
+        <v>300</v>
+      </c>
+      <c r="K13" s="29">
+        <v>0.5</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="M13" s="30">
         <v>3.5</v>
@@ -5589,34 +5763,103 @@
         <v>0</v>
       </c>
       <c r="Q13" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R13" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S13" s="28"/>
       <c r="T13" s="14"/>
       <c r="U13" s="14" t="s">
-        <v>297</v>
+        <v>302</v>
+      </c>
+      <c r="V13" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="W13" s="14"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="K14" s="31">
+        <v>1</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="M14" s="26">
+        <v>3.5</v>
+      </c>
+      <c r="N14" s="24">
+        <v>0</v>
+      </c>
+      <c r="O14" s="24">
+        <v>0</v>
+      </c>
+      <c r="P14" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="R14" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="S14" s="28"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:U13"/>
+  <autoFilter ref="A3:W14"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="Q10:Q13">
+    <dataValidation type="list" sqref="Q10:Q14">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Q4:Q13">
+    <dataValidation type="list" sqref="Q4:Q14">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R10:R13">
+    <dataValidation type="list" sqref="R10:R14">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R4:R13">
+    <dataValidation type="list" sqref="R4:R14">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5633,25 +5876,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="10" width="16" customWidth="1"/>
-    <col min="11" max="13" width="30" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="12" width="16" customWidth="1"/>
+    <col min="13" max="15" width="30" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -5668,10 +5912,12 @@
       <c r="N1" s="32"/>
       <c r="O1" s="32"/>
       <c r="P1" s="32"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -5688,204 +5934,282 @@
       <c r="N2" s="33"/>
       <c r="O2" s="33"/>
       <c r="P2" s="33"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>300</v>
+        <v>212</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="E3" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="H3" s="21" t="s">
+      <c r="C4" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="J3" s="21" t="s">
+      <c r="F4" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D4" s="24" t="s">
+      <c r="J7" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="N7" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24" t="s">
-        <v>333</v>
+      <c r="O7" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P6"/>
+  <autoFilter ref="A3:R7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5900,23 +6224,25 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="7" width="16" customWidth="1"/>
-    <col min="8" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="36" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="9" width="16" customWidth="1"/>
+    <col min="10" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="36" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -5930,10 +6256,12 @@
       <c r="K1" s="32"/>
       <c r="L1" s="32"/>
       <c r="M1" s="32"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -5947,170 +6275,233 @@
       <c r="K2" s="33"/>
       <c r="L2" s="33"/>
       <c r="M2" s="33"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="F3" s="21" t="s">
+      <c r="C4" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="I3" s="21" t="s">
+      <c r="F4" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24" t="s">
+      <c r="E7" s="14"/>
+      <c r="F7" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="L7" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="M4" s="24" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>342</v>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M6"/>
+  <autoFilter ref="A3:O7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6125,7 +6516,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6162,13 +6553,15 @@
     <col min="38" max="43" width="18" customWidth="1"/>
     <col min="44" max="44" width="30" customWidth="1"/>
     <col min="45" max="45" width="18" customWidth="1"/>
-    <col min="46" max="46" width="36" customWidth="1"/>
-    <col min="47" max="47" width="16" customWidth="1"/>
+    <col min="46" max="46" width="16" customWidth="1"/>
+    <col min="47" max="47" width="38" customWidth="1"/>
+    <col min="48" max="48" width="36" customWidth="1"/>
+    <col min="49" max="49" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6216,10 +6609,12 @@
       <c r="AS1" s="19"/>
       <c r="AT1" s="19"/>
       <c r="AU1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV1" s="19"/>
+      <c r="AW1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6267,8 +6662,10 @@
       <c r="AS2" s="20"/>
       <c r="AT2" s="20"/>
       <c r="AU2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -6282,94 +6679,94 @@
         <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>31</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="I3" s="35" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="J3" s="21" t="s">
         <v>40</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="M3" s="21" t="s">
         <v>34</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="V3" s="21" t="s">
         <v>46</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="X3" s="21" t="s">
         <v>91</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>65</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="AE3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="AH3" s="23" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="AI3" s="22" t="s">
         <v>202</v>
@@ -6378,7 +6775,7 @@
         <v>203</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="AL3" s="21" t="s">
         <v>205</v>
@@ -6390,7 +6787,7 @@
         <v>207</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AP3" s="21" t="s">
         <v>208</v>
@@ -6408,108 +6805,114 @@
         <v>212</v>
       </c>
       <c r="AU3" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="AV3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW3" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>81</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I4" s="37">
         <v>520</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="V4" s="36" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="W4" s="36" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="X4" s="24" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z4" s="24" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="AA4" s="24" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="AB4" s="24" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="AC4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AD4" s="24" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="AE4" s="24" t="s">
         <v>86</v>
       </c>
       <c r="AF4" s="24" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG4" s="24" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AH4" s="26">
         <v>4.1</v>
@@ -6518,10 +6921,10 @@
         <v>0.2222222222222222</v>
       </c>
       <c r="AJ4" s="24" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AK4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AL4" s="24">
         <v>0</v>
@@ -6534,23 +6937,27 @@
       </c>
       <c r="AO4" s="24"/>
       <c r="AP4" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AQ4" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AR4" s="28"/>
       <c r="AS4" s="24"/>
-      <c r="AT4" s="24"/>
-      <c r="AU4" s="24" t="s">
-        <v>385</v>
+      <c r="AT4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AU4"/>
+  <autoFilter ref="A3:AW4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AU1"/>
-    <mergeCell ref="A2:AU2"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A2:AW2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="AP4">
@@ -6573,7 +6980,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AK4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6597,13 +7004,15 @@
     <col min="26" max="31" width="18" customWidth="1"/>
     <col min="32" max="32" width="30" customWidth="1"/>
     <col min="33" max="33" width="18" customWidth="1"/>
-    <col min="34" max="34" width="36" customWidth="1"/>
-    <col min="35" max="35" width="16" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+    <col min="35" max="35" width="38" customWidth="1"/>
+    <col min="36" max="36" width="36" customWidth="1"/>
+    <col min="37" max="37" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6639,10 +7048,12 @@
       <c r="AG1" s="19"/>
       <c r="AH1" s="19"/>
       <c r="AI1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -6678,8 +7089,10 @@
       <c r="AG2" s="20"/>
       <c r="AH2" s="20"/>
       <c r="AI2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -6693,58 +7106,58 @@
         <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="35" t="s">
+        <v>415</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="P3" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>363</v>
-      </c>
       <c r="Q3" s="21" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="S3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="V3" s="23" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="W3" s="22" t="s">
         <v>202</v>
@@ -6753,7 +7166,7 @@
         <v>203</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>205</v>
@@ -6765,7 +7178,7 @@
         <v>207</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AD3" s="21" t="s">
         <v>208</v>
@@ -6783,72 +7196,78 @@
         <v>212</v>
       </c>
       <c r="AI3" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK3" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E4" s="36" t="s">
         <v>92</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="H4" s="37">
         <v>80</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="S4" s="24" t="s">
         <v>86</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="V4" s="26">
         <v>4.4</v>
@@ -6857,10 +7276,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="X4" s="24" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z4" s="24">
         <v>0</v>
@@ -6873,23 +7292,27 @@
       </c>
       <c r="AC4" s="24"/>
       <c r="AD4" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AE4" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AF4" s="28"/>
       <c r="AG4" s="24"/>
-      <c r="AH4" s="24"/>
-      <c r="AI4" s="24" t="s">
-        <v>400</v>
+      <c r="AH4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AI4"/>
+  <autoFilter ref="A3:AK4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:AK2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="AD4">
@@ -6912,7 +7335,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AS5"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6938,13 +7361,15 @@
     <col min="34" max="39" width="18" customWidth="1"/>
     <col min="40" max="40" width="30" customWidth="1"/>
     <col min="41" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="36" customWidth="1"/>
-    <col min="43" max="43" width="16" customWidth="1"/>
+    <col min="42" max="42" width="16" customWidth="1"/>
+    <col min="43" max="43" width="38" customWidth="1"/>
+    <col min="44" max="44" width="36" customWidth="1"/>
+    <col min="45" max="45" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -6988,10 +7413,12 @@
       <c r="AO1" s="19"/>
       <c r="AP1" s="19"/>
       <c r="AQ1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AR1" s="19"/>
+      <c r="AS1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7035,8 +7462,10 @@
       <c r="AO2" s="20"/>
       <c r="AP2" s="20"/>
       <c r="AQ2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -7044,7 +7473,7 @@
         <v>195</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>194</v>
@@ -7053,79 +7482,79 @@
         <v>199</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="35" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="W3" s="21" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="AB3" s="21" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="AE3" s="22" t="s">
         <v>202</v>
@@ -7134,7 +7563,7 @@
         <v>203</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="AH3" s="21" t="s">
         <v>205</v>
@@ -7146,7 +7575,7 @@
         <v>207</v>
       </c>
       <c r="AK3" s="21" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AL3" s="21" t="s">
         <v>208</v>
@@ -7164,106 +7593,114 @@
         <v>212</v>
       </c>
       <c r="AQ3" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="AR3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AS3" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>418</v>
+        <v>256</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E4" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="F4" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="F4" s="36" t="s">
-        <v>283</v>
-      </c>
       <c r="G4" s="36" t="s">
-        <v>419</v>
-      </c>
-      <c r="H4" s="37"/>
+        <v>256</v>
+      </c>
+      <c r="H4" s="37">
+        <v>200</v>
+      </c>
       <c r="I4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>422</v>
+        <v>256</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="V4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="W4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="X4" s="24" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA4" s="24" t="s">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="AB4" s="24" t="s">
-        <v>287</v>
+        <v>448</v>
       </c>
       <c r="AC4" s="24" t="s">
-        <v>288</v>
+        <v>449</v>
       </c>
       <c r="AD4" s="26">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AE4" s="29">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AF4" s="24" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG4" s="24" t="s">
-        <v>253</v>
+        <v>450</v>
       </c>
       <c r="AH4" s="24">
         <v>0</v>
@@ -7276,29 +7713,160 @@
       </c>
       <c r="AK4" s="24"/>
       <c r="AL4" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM4" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AN4" s="28"/>
       <c r="AO4" s="24"/>
-      <c r="AP4" s="24"/>
+      <c r="AP4" s="24" t="s">
+        <v>302</v>
+      </c>
       <c r="AQ4" s="24" t="s">
-        <v>425</v>
+        <v>303</v>
+      </c>
+      <c r="AR4" s="24"/>
+      <c r="AS4" s="24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>453</v>
+      </c>
+      <c r="H5" s="37"/>
+      <c r="I5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="J5" s="36" t="s">
+        <v>454</v>
+      </c>
+      <c r="K5" s="36" t="s">
+        <v>455</v>
+      </c>
+      <c r="L5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="M5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="N5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="S5" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="T5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X5" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="Y5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA5" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB5" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="AD5" s="30">
+        <v>3.8</v>
+      </c>
+      <c r="AE5" s="29">
+        <v>0.6</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AH5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="14"/>
+      <c r="AL5" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="AM5" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="14"/>
+      <c r="AP5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="AQ5" s="14"/>
+      <c r="AR5" s="14"/>
+      <c r="AS5" s="14" t="s">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AQ4"/>
+  <autoFilter ref="A3:AS5"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AQ1"/>
-    <mergeCell ref="A2:AQ2"/>
+    <mergeCell ref="A1:AS1"/>
+    <mergeCell ref="A2:AS2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="AL4">
+    <dataValidation type="list" sqref="AL4:AL5">
       <formula1>"待比较,备选,拟定,淘汰"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AM4">
+    <dataValidation type="list" sqref="AM4:AM5">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7315,7 +7883,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AO4"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7342,13 +7910,15 @@
     <col min="30" max="35" width="18" customWidth="1"/>
     <col min="36" max="36" width="30" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="36" customWidth="1"/>
-    <col min="39" max="39" width="16" customWidth="1"/>
+    <col min="38" max="38" width="16" customWidth="1"/>
+    <col min="39" max="39" width="38" customWidth="1"/>
+    <col min="40" max="40" width="36" customWidth="1"/>
+    <col min="41" max="41" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7388,10 +7958,12 @@
       <c r="AK1" s="19"/>
       <c r="AL1" s="19"/>
       <c r="AM1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7431,8 +8003,10 @@
       <c r="AK2" s="20"/>
       <c r="AL2" s="20"/>
       <c r="AM2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -7446,70 +8020,70 @@
         <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>31</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="P3" s="21" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="Q3" s="21" t="s">
         <v>34</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="T3" s="21" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="W3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="Z3" s="23" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="AA3" s="22" t="s">
         <v>202</v>
@@ -7518,7 +8092,7 @@
         <v>203</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="AD3" s="21" t="s">
         <v>205</v>
@@ -7530,7 +8104,7 @@
         <v>207</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AH3" s="21" t="s">
         <v>208</v>
@@ -7548,7 +8122,13 @@
         <v>212</v>
       </c>
       <c r="AM3" s="21" t="s">
-        <v>370</v>
+        <v>213</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO3" s="21" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="34:36" x14ac:dyDescent="0.25">
@@ -7557,10 +8137,10 @@
       <c r="AJ4" s="39"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AM4"/>
+  <autoFilter ref="A3:AO4"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AM1"/>
-    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="A2:AO2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="AH4">
@@ -7583,7 +8163,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF7"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7605,13 +8185,15 @@
     <col min="23" max="28" width="18" customWidth="1"/>
     <col min="29" max="29" width="30" customWidth="1"/>
     <col min="30" max="30" width="18" customWidth="1"/>
-    <col min="31" max="31" width="36" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="31" max="31" width="16" customWidth="1"/>
+    <col min="32" max="32" width="38" customWidth="1"/>
+    <col min="33" max="33" width="36" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7644,10 +8226,12 @@
       <c r="AD1" s="19"/>
       <c r="AE1" s="19"/>
       <c r="AF1" s="19"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -7680,8 +8264,10 @@
       <c r="AD2" s="20"/>
       <c r="AE2" s="20"/>
       <c r="AF2" s="20"/>
-    </row>
-    <row r="3" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
@@ -7695,49 +8281,49 @@
         <v>199</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>31</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="P3" s="21" t="s">
         <v>67</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="R3" s="21" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="T3" s="22" t="s">
         <v>202</v>
@@ -7746,7 +8332,7 @@
         <v>203</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="W3" s="21" t="s">
         <v>205</v>
@@ -7758,7 +8344,7 @@
         <v>207</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>208</v>
@@ -7776,61 +8362,67 @@
         <v>212</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="AH3" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>99</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G4" s="37"/>
       <c r="H4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="P4" s="24" t="s">
         <v>78</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S4" s="26">
         <v>4.8</v>
@@ -7839,10 +8431,10 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="V4" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="W4" s="24">
         <v>0</v>
@@ -7855,72 +8447,76 @@
       </c>
       <c r="Z4" s="24"/>
       <c r="AA4" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AB4" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AC4" s="28"/>
       <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AE4" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>99</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G5" s="37">
         <v>0</v>
       </c>
       <c r="H5" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="P5" s="14" t="s">
         <v>78</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R5" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="S5" s="30">
         <v>4.3</v>
@@ -7929,10 +8525,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="U5" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="W5" s="14">
         <v>0</v>
@@ -7945,27 +8541,31 @@
       </c>
       <c r="Z5" s="14"/>
       <c r="AA5" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AB5" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AC5" s="28"/>
       <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AE5" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>99</v>
@@ -7978,37 +8578,37 @@
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L6" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M6" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="P6" s="24" t="s">
         <v>78</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="S6" s="26">
         <v>4.6</v>
@@ -8017,10 +8617,10 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="U6" s="24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="V6" s="24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="W6" s="24">
         <v>0</v>
@@ -8033,21 +8633,25 @@
       </c>
       <c r="Z6" s="24"/>
       <c r="AA6" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AB6" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AC6" s="28"/>
       <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AE6" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B7" s="36" t="s">
         <v>142</v>
@@ -8056,49 +8660,49 @@
         <v>141</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G7" s="37">
         <v>0</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J7" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L7" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M7" s="36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="P7" s="14" t="s">
         <v>78</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="R7" s="14" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="S7" s="30">
         <v>4.7</v>
@@ -8107,10 +8711,10 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="U7" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V7" s="14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="W7" s="14">
         <v>0</v>
@@ -8123,23 +8727,27 @@
       </c>
       <c r="Z7" s="14"/>
       <c r="AA7" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AB7" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AC7" s="28"/>
       <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
-      <c r="AF7" s="14" t="s">
-        <v>447</v>
+      <c r="AE7" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AF7"/>
+  <autoFilter ref="A3:AH7"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A2:AF2"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A2:AH2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="AA4:AA7">
